--- a/outputs/scenario_summary.xlsx
+++ b/outputs/scenario_summary.xlsx
@@ -51987,7 +51987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B84"/>
+  <dimension ref="A1:B82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -52761,7 +52761,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>hurdle_completion_trigger.execute_only_if_lp_fully_redeemed</t>
+          <t>backend_liquidity_strategy.enabled</t>
         </is>
       </c>
       <c r="B76" t="b">
@@ -52771,82 +52771,62 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>backend_liquidity_strategy.enabled</t>
-        </is>
-      </c>
-      <c r="B77" t="b">
-        <v>1</v>
+          <t>backend_liquidity_strategy.target_years</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>[5, 7, 10]</t>
+        </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>backend_liquidity_strategy.target_years</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>[5, 7, 10]</t>
-        </is>
+          <t>backend_liquidity_strategy.refi_first</t>
+        </is>
+      </c>
+      <c r="B78" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>backend_liquidity_strategy.refi_first</t>
-        </is>
-      </c>
-      <c r="B79" t="b">
-        <v>1</v>
+          <t>backend_liquidity_strategy.max_refi_pct_of_re_nav</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>0.35</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>backend_liquidity_strategy.max_refi_pct_of_re_nav</t>
+          <t>backend_liquidity_strategy.max_hf_liquidation_pct</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>backend_liquidity_strategy.max_hf_liquidation_pct</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
-        <v>0.5</v>
+          <t>backend_liquidity_strategy.use_retained_cash</t>
+        </is>
+      </c>
+      <c r="B81" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>backend_liquidity_strategy.use_retained_cash</t>
+          <t>backend_liquidity_strategy.use_reserve</t>
         </is>
       </c>
       <c r="B82" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>backend_liquidity_strategy.use_reserve</t>
-        </is>
-      </c>
-      <c r="B83" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>backend_liquidity_strategy.execute_only_if_lp_hurdle_completed</t>
-        </is>
-      </c>
-      <c r="B84" t="b">
         <v>1</v>
       </c>
     </row>

--- a/outputs/scenario_summary.xlsx
+++ b/outputs/scenario_summary.xlsx
@@ -48,7 +48,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -56,13 +56,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -431,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG12"/>
+  <dimension ref="A1:CG13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -3032,7 +3040,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Equinox on Indian School base case — Sandpainter underwriting Apr 2026. 116-unit Phoenix value-add. $23M purchase, $3.5M equity, $16M new senior + $2.5M assumed liabilities. NOI $1.28M Y1 ramping to $2.15M stabilized. 7.5% IO debt. Refi Y4/Y7 at 70% LTV. HF 13% base. Cashflow routing 60/25/15.</t>
+          <t>Deal 1 base case — 116-unit Class C value-add multifamily, Southwest US. $23M purchase, $3.5M equity, $16M senior + $2.5M assumed liabilities. NOI $1.28M Y1 ramping to $2.15M stabilized. 7.5% IO debt. Refi Y4/Y7 at 70% LTV. HF 13% base. Cashflow routing 60/25/15.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3299,7 +3307,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Equinox downside — slower lease-up, lower NOI ramp, higher capex, tighter refi. HF -15% Y1 then recovery.</t>
+          <t>Deal 1 downside — slower lease-up, lower NOI ramp, higher capex, tighter refi. HF -15% Y1 then recovery.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3561,12 +3569,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>jon_upside_case</t>
+          <t>jon_property_shock</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Equinox upside — faster lease-up, stronger NOI, 5% value growth, better HF returns (25%).</t>
+          <t>Deal 1 property shock — 25% value drop in Year 2 (market correction), 5-year recovery back to pre-shock trajectory. HF 13% base. Cashflow routing 60/25/15.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -3599,7 +3607,7 @@
         <v>1.285714285714286</v>
       </c>
       <c r="L12" t="n">
-        <v>29354475.93750001</v>
+        <v>24374928.43931933</v>
       </c>
       <c r="M12" t="n">
         <v>16000000</v>
@@ -3608,19 +3616,19 @@
         <v>2500000</v>
       </c>
       <c r="O12" t="n">
-        <v>10854475.93750001</v>
+        <v>5874928.439319327</v>
       </c>
       <c r="P12" t="n">
-        <v>2.343466666666667</v>
+        <v>2.077032716454167</v>
       </c>
       <c r="Q12" t="n">
-        <v>7200000</v>
+        <v>10800000</v>
       </c>
       <c r="R12" t="n">
-        <v>1252904</v>
+        <v>2044523.2500498</v>
       </c>
       <c r="S12" t="n">
-        <v>2598196.0625</v>
+        <v>0</v>
       </c>
       <c r="T12" s="2" t="n">
         <v>0</v>
@@ -3641,7 +3649,7 @@
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AA12" s="3" t="n">
         <v>2</v>
@@ -3659,13 +3667,13 @@
         <v>2</v>
       </c>
       <c r="AF12" s="4" t="n">
-        <v>0.1296871006142786</v>
+        <v>0.08532638668638093</v>
       </c>
       <c r="AG12" s="4" t="n">
-        <v>0.1296871006142786</v>
+        <v>0.08532638668638093</v>
       </c>
       <c r="AH12" s="4" t="n">
-        <v>0.1296871006142786</v>
+        <v>0.08532638668638093</v>
       </c>
       <c r="AI12" s="4" t="inlineStr"/>
       <c r="AJ12" s="3" t="inlineStr"/>
@@ -3673,31 +3681,31 @@
         <v>1</v>
       </c>
       <c r="AL12" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AM12" s="2" t="b">
         <v>1</v>
       </c>
       <c r="AN12" s="2" t="n">
-        <v>13040412.953125</v>
+        <v>9170565.794856433</v>
       </c>
       <c r="AO12" s="2" t="n">
-        <v>2598196.0625</v>
+        <v>1157117.358123071</v>
       </c>
       <c r="AP12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AQ12" s="2" t="n">
-        <v>13040412.953125</v>
+        <v>9170565.794856433</v>
       </c>
       <c r="AR12" s="2" t="n">
-        <v>13040412.953125</v>
+        <v>9170565.794856433</v>
       </c>
       <c r="AS12" s="4" t="n">
-        <v>1.3040412953125</v>
+        <v>0.9170565794856432</v>
       </c>
       <c r="AT12" s="4" t="n">
-        <v>1.3040412953125</v>
+        <v>0.9170565794856432</v>
       </c>
       <c r="AU12" s="2" t="n">
         <v>0</v>
@@ -3709,25 +3717,25 @@
         <v>1</v>
       </c>
       <c r="AX12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC12" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD12" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="AY12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB12" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC12" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD12" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="BE12" s="2" t="n">
         <v>0</v>
@@ -3736,22 +3744,22 @@
         <v>1</v>
       </c>
       <c r="BG12" s="4" t="n">
-        <v>5750756</v>
+        <v>6335758.0011952</v>
       </c>
       <c r="BH12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="BI12" t="n">
-        <v>1437689</v>
+        <v>1583939.5002988</v>
       </c>
       <c r="BJ12" t="n">
         <v>20000000</v>
       </c>
       <c r="BK12" t="n">
-        <v>862613.4</v>
+        <v>950363.70017928</v>
       </c>
       <c r="BL12" s="4" t="n">
-        <v>3.477803613994404</v>
+        <v>3.156686223846796</v>
       </c>
       <c r="BM12" s="4" t="n">
         <v>0.25</v>
@@ -3760,10 +3768,10 @@
         <v>0.15</v>
       </c>
       <c r="BO12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BP12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BQ12" s="2" t="inlineStr">
         <is>
@@ -3794,32 +3802,299 @@
         <v>1</v>
       </c>
       <c r="BY12" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>1683163.70017928</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>13358264.14098053</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>1157117.358123071</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>HURDLE_COMPLETION_TRIGGER_EXECUTED</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
+          <t>LP_HURDLE_ACHIEVED; HURDLE_REACHED_BUT_LIQUIDITY_CONSTRAINED; SLOW_TIME_HORIZON_DRIFT; GP_SURVIVABILITY_RISK; HURDLE_COMPLETION_TRIGGER_EXECUTED; HURDLE_TRIGGER_ATTEMPTED_BUT_INSUFFICIENT; LP_REDEEMED_VIA_HF_LIQUIDATION; LP_REDEEMED_VIA_REFI; RE_NAV_IMPAIRMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>jon_upside_case</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Deal 1 upside — faster lease-up, stronger NOI, 5% value growth, better HF returns (25%).</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>bottom_up</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="F13" t="n">
+        <v>23000000</v>
+      </c>
+      <c r="G13" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>1.285714285714286</v>
+      </c>
+      <c r="L13" t="n">
+        <v>29354475.93750001</v>
+      </c>
+      <c r="M13" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="O13" t="n">
+        <v>10854475.93750001</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.343466666666667</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1252904</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2598196.0625</v>
+      </c>
+      <c r="T13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
         <v>6</v>
       </c>
-      <c r="BZ12" t="n">
+      <c r="AA13" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB13" s="2" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AC13" s="2" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AD13" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE13" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF13" s="4" t="n">
+        <v>0.1296871006142786</v>
+      </c>
+      <c r="AG13" s="4" t="n">
+        <v>0.1296871006142786</v>
+      </c>
+      <c r="AH13" s="4" t="n">
+        <v>0.1296871006142786</v>
+      </c>
+      <c r="AI13" s="4" t="inlineStr"/>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL13" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AM13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN13" s="2" t="n">
+        <v>13040412.953125</v>
+      </c>
+      <c r="AO13" s="2" t="n">
         <v>2598196.0625</v>
       </c>
-      <c r="CA12" t="n">
+      <c r="AP13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="2" t="n">
+        <v>13040412.953125</v>
+      </c>
+      <c r="AR13" s="2" t="n">
+        <v>13040412.953125</v>
+      </c>
+      <c r="AS13" s="4" t="n">
+        <v>1.3040412953125</v>
+      </c>
+      <c r="AT13" s="4" t="n">
+        <v>1.3040412953125</v>
+      </c>
+      <c r="AU13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC13" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="b">
+        <v>1</v>
+      </c>
+      <c r="BG13" s="4" t="n">
+        <v>5750756</v>
+      </c>
+      <c r="BH13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>1437689</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>862613.4</v>
+      </c>
+      <c r="BL13" s="4" t="n">
+        <v>3.477803613994404</v>
+      </c>
+      <c r="BM13" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BN13" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BQ13" s="2" t="inlineStr">
+        <is>
+          <t>BACKEND_HEAVY</t>
+        </is>
+      </c>
+      <c r="BR13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BS13" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="BT13" s="2" t="inlineStr">
+        <is>
+          <t>5, 7, 10</t>
+        </is>
+      </c>
+      <c r="BU13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BV13" s="4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BW13" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BX13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BY13" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>2598196.0625</v>
+      </c>
+      <c r="CA13" t="n">
         <v>2075113.4</v>
       </c>
-      <c r="CB12" t="n">
+      <c r="CB13" t="n">
         <v>11876236.9375</v>
       </c>
-      <c r="CC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF12" t="inlineStr">
+      <c r="CC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF13" t="inlineStr">
         <is>
           <t>HURDLE_COMPLETION_TRIGGER_EXECUTED</t>
         </is>
       </c>
-      <c r="CG12" t="inlineStr">
+      <c r="CG13" t="inlineStr">
         <is>
           <t>LP_HURDLE_ACHIEVED; HURDLE_REACHED_BUT_LIQUIDITY_CONSTRAINED; GP_SURVIVABILITY_RISK; HURDLE_COMPLETION_TRIGGER_EXECUTED; HURDLE_TRIGGER_ATTEMPTED_BUT_INSUFFICIENT; LP_REDEEMED_VIA_HF_LIQUIDATION; REFINANCE_EVENT_OCCURRED; LP_GOOD_IRR_GP_LARGE_RESIDUAL</t>
         </is>
@@ -3836,7 +4111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CQ152"/>
+  <dimension ref="A1:CQ161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -45062,7 +45337,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>jon_upside_case</t>
+          <t>jon_property_shock</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -45089,10 +45364,10 @@
         <v>4500000</v>
       </c>
       <c r="I147" s="4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.284</v>
       </c>
       <c r="J147" s="2" t="n">
-        <v>1500000</v>
+        <v>1278000</v>
       </c>
       <c r="K147" s="2" t="n">
         <v>0</v>
@@ -45101,10 +45376,10 @@
         <v>1200000</v>
       </c>
       <c r="M147" t="n">
-        <v>387500</v>
+        <v>551120</v>
       </c>
       <c r="N147" t="n">
-        <v>1.25</v>
+        <v>1.065</v>
       </c>
       <c r="O147" s="2" t="n">
         <v>0</v>
@@ -45119,16 +45394,16 @@
         <v>99999.99999999814</v>
       </c>
       <c r="S147" t="n">
-        <v>1499.999999999972</v>
+        <v>2499.999999999954</v>
       </c>
       <c r="T147" t="n">
-        <v>98499.99999999817</v>
+        <v>97499.99999999818</v>
       </c>
       <c r="U147" t="n">
         <v>0</v>
       </c>
       <c r="V147" s="2" t="n">
-        <v>-87500</v>
+        <v>-473120</v>
       </c>
       <c r="W147" s="2" t="n">
         <v>0</v>
@@ -45175,7 +45450,7 @@
         <v>0</v>
       </c>
       <c r="AK147" s="2" t="n">
-        <v>-87500</v>
+        <v>-473120</v>
       </c>
       <c r="AL147" s="4" t="n">
         <v>0</v>
@@ -45199,7 +45474,7 @@
         <v>5200000</v>
       </c>
       <c r="AS147" s="4" t="n">
-        <v>0.25</v>
+        <v>0.13</v>
       </c>
       <c r="AT147" t="n">
         <v>0</v>
@@ -45217,7 +45492,7 @@
         <v>0</v>
       </c>
       <c r="AY147" s="2" t="n">
-        <v>6500000</v>
+        <v>5875999.999999999</v>
       </c>
       <c r="AZ147" t="n">
         <v>0</v>
@@ -45232,7 +45507,7 @@
         <v>1300000</v>
       </c>
       <c r="BE147" s="2" t="n">
-        <v>1212500</v>
+        <v>826880</v>
       </c>
       <c r="BF147" t="n">
         <v>0</v>
@@ -45287,7 +45562,7 @@
         <v>0</v>
       </c>
       <c r="BX147" s="2" t="n">
-        <v>8837500</v>
+        <v>7827879.999999999</v>
       </c>
       <c r="BY147" s="2" t="b">
         <v>0</v>
@@ -45341,13 +45616,13 @@
         <v>0</v>
       </c>
       <c r="CP147" s="2" t="n">
-        <v>12212500</v>
+        <v>11202880</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>jon_upside_case</t>
+          <t>jon_property_shock</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -45362,7 +45637,7 @@
         <v>4500000</v>
       </c>
       <c r="E148" t="n">
-        <v>24150000</v>
+        <v>23690000</v>
       </c>
       <c r="F148" t="n">
         <v>16000000</v>
@@ -45371,13 +45646,13 @@
         <v>2500000</v>
       </c>
       <c r="H148" t="n">
-        <v>5650000</v>
+        <v>5190000</v>
       </c>
       <c r="I148" s="4" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.3485925925925926</v>
       </c>
       <c r="J148" s="2" t="n">
-        <v>2000000</v>
+        <v>1568666.666666667</v>
       </c>
       <c r="K148" s="2" t="n">
         <v>0</v>
@@ -45386,10 +45661,10 @@
         <v>1200000</v>
       </c>
       <c r="M148" t="n">
-        <v>300000</v>
+        <v>462746.6666666667</v>
       </c>
       <c r="N148" t="n">
-        <v>1.666666666666667</v>
+        <v>1.307222222222222</v>
       </c>
       <c r="O148" s="2" t="n">
         <v>0</v>
@@ -45398,22 +45673,22 @@
         <v>0</v>
       </c>
       <c r="Q148" t="n">
-        <v>16905000</v>
+        <v>16583000</v>
       </c>
       <c r="R148" t="n">
-        <v>905000</v>
+        <v>582999.9999999981</v>
       </c>
       <c r="S148" t="n">
-        <v>13575</v>
+        <v>14574.99999999995</v>
       </c>
       <c r="T148" t="n">
-        <v>891425</v>
+        <v>568424.9999999981</v>
       </c>
       <c r="U148" t="n">
         <v>0</v>
       </c>
       <c r="V148" s="2" t="n">
-        <v>500000</v>
+        <v>-94080.00000000017</v>
       </c>
       <c r="W148" s="2" t="n">
         <v>0</v>
@@ -45425,7 +45700,7 @@
         <v>0</v>
       </c>
       <c r="Z148" t="n">
-        <v>1212500</v>
+        <v>826880</v>
       </c>
       <c r="AA148" t="n">
         <v>0</v>
@@ -45449,37 +45724,37 @@
         <v>0</v>
       </c>
       <c r="AH148" t="n">
-        <v>1212500</v>
+        <v>826880</v>
       </c>
       <c r="AJ148" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AK148" s="2" t="n">
-        <v>500000</v>
+        <v>-94080.00000000017</v>
       </c>
       <c r="AL148" s="4" t="n">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="AM148" s="2" t="n">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="AN148" s="2" t="n">
-        <v>125000</v>
+        <v>0</v>
       </c>
       <c r="AO148" s="2" t="n">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="AP148" s="4" t="n">
-        <v>0.2555555555555555</v>
+        <v>0.1533333333333333</v>
       </c>
       <c r="AQ148" s="2" t="n">
-        <v>5650000</v>
+        <v>5190000</v>
       </c>
       <c r="AR148" s="2" t="n">
-        <v>6500000</v>
+        <v>5875999.999999999</v>
       </c>
       <c r="AS148" s="4" t="n">
-        <v>0.25</v>
+        <v>0.13</v>
       </c>
       <c r="AT148" t="n">
         <v>0</v>
@@ -45497,7 +45772,7 @@
         <v>0</v>
       </c>
       <c r="AY148" s="2" t="n">
-        <v>8250000</v>
+        <v>6639879.999999998</v>
       </c>
       <c r="AZ148" t="n">
         <v>0</v>
@@ -45509,10 +45784,10 @@
         <v>0</v>
       </c>
       <c r="BD148" s="2" t="n">
-        <v>1212500</v>
+        <v>826880</v>
       </c>
       <c r="BE148" s="2" t="n">
-        <v>1287500</v>
+        <v>732799.9999999998</v>
       </c>
       <c r="BF148" t="n">
         <v>0</v>
@@ -45531,43 +45806,43 @@
       </c>
       <c r="BK148" s="4" t="inlineStr"/>
       <c r="BL148" t="n">
-        <v>125000</v>
+        <v>0</v>
       </c>
       <c r="BM148" t="n">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="BN148" t="n">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="BO148" t="n">
-        <v>125000</v>
+        <v>0</v>
       </c>
       <c r="BP148" t="n">
         <v>0</v>
       </c>
       <c r="BQ148" t="n">
-        <v>125000</v>
+        <v>0</v>
       </c>
       <c r="BR148" t="n">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="BS148" t="n">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="BT148" s="2" t="n">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="BU148" s="2" t="n">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="BV148" s="2" t="n">
-        <v>19700000</v>
+        <v>20000000</v>
       </c>
       <c r="BW148" s="2" t="b">
         <v>0</v>
       </c>
       <c r="BX148" s="2" t="n">
-        <v>10950000</v>
+        <v>8670179.999999998</v>
       </c>
       <c r="BY148" s="2" t="b">
         <v>0</v>
@@ -45582,7 +45857,7 @@
         <v>0</v>
       </c>
       <c r="CC148" s="2" t="n">
-        <v>19700000</v>
+        <v>20000000</v>
       </c>
       <c r="CD148" t="n">
         <v>0</v>
@@ -45600,7 +45875,7 @@
         <v>0</v>
       </c>
       <c r="CI148" s="2" t="n">
-        <v>19700000</v>
+        <v>20000000</v>
       </c>
       <c r="CJ148" s="2" t="n">
         <v>0</v>
@@ -45621,13 +45896,13 @@
         <v>0</v>
       </c>
       <c r="CP148" s="2" t="n">
-        <v>15187500</v>
+        <v>12562680</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>jon_upside_case</t>
+          <t>jon_property_shock</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -45639,10 +45914,10 @@
         </is>
       </c>
       <c r="D149" s="2" t="n">
-        <v>5650000</v>
+        <v>5190000</v>
       </c>
       <c r="E149" t="n">
-        <v>25357500</v>
+        <v>17767500</v>
       </c>
       <c r="F149" t="n">
         <v>16000000</v>
@@ -45651,13 +45926,13 @@
         <v>2500000</v>
       </c>
       <c r="H149" t="n">
-        <v>6857500</v>
+        <v>-732500</v>
       </c>
       <c r="I149" s="4" t="n">
-        <v>0.4424778761061947</v>
+        <v>0.3582530507385999</v>
       </c>
       <c r="J149" s="2" t="n">
-        <v>2500000</v>
+        <v>1859333.333333333</v>
       </c>
       <c r="K149" s="2" t="n">
         <v>0</v>
@@ -45666,10 +45941,10 @@
         <v>1200000</v>
       </c>
       <c r="M149" t="n">
-        <v>212500</v>
+        <v>324373.3333333333</v>
       </c>
       <c r="N149" t="n">
-        <v>2.083333333333333</v>
+        <v>1.549444444444444</v>
       </c>
       <c r="O149" s="2" t="n">
         <v>0</v>
@@ -45678,22 +45953,22 @@
         <v>0</v>
       </c>
       <c r="Q149" t="n">
-        <v>17750250</v>
+        <v>12437250</v>
       </c>
       <c r="R149" t="n">
-        <v>1750250</v>
+        <v>-3562750</v>
       </c>
       <c r="S149" t="n">
-        <v>26253.75</v>
+        <v>0</v>
       </c>
       <c r="T149" t="n">
-        <v>1723996.25</v>
+        <v>0</v>
       </c>
       <c r="U149" t="n">
         <v>0</v>
       </c>
       <c r="V149" s="2" t="n">
-        <v>1087500</v>
+        <v>334959.9999999999</v>
       </c>
       <c r="W149" s="2" t="n">
         <v>0</v>
@@ -45705,7 +45980,7 @@
         <v>0</v>
       </c>
       <c r="Z149" t="n">
-        <v>1287500</v>
+        <v>732799.9999999998</v>
       </c>
       <c r="AA149" t="n">
         <v>0</v>
@@ -45729,37 +46004,37 @@
         <v>0</v>
       </c>
       <c r="AH149" t="n">
-        <v>1287500</v>
+        <v>732799.9999999998</v>
       </c>
       <c r="AJ149" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AK149" s="2" t="n">
-        <v>1087500</v>
+        <v>334959.9999999999</v>
       </c>
       <c r="AL149" s="4" t="n">
-        <v>1087500</v>
+        <v>334959.9999999999</v>
       </c>
       <c r="AM149" s="2" t="n">
-        <v>652500</v>
+        <v>200976</v>
       </c>
       <c r="AN149" s="2" t="n">
-        <v>271875</v>
+        <v>83739.99999999999</v>
       </c>
       <c r="AO149" s="2" t="n">
-        <v>163125</v>
+        <v>50243.99999999999</v>
       </c>
       <c r="AP149" s="4" t="n">
-        <v>0.213716814159292</v>
+        <v>-1.141136801541426</v>
       </c>
       <c r="AQ149" s="2" t="n">
-        <v>6857500</v>
+        <v>-732500</v>
       </c>
       <c r="AR149" s="2" t="n">
-        <v>8250000</v>
+        <v>6639879.999999998</v>
       </c>
       <c r="AS149" s="4" t="n">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="AT149" t="n">
         <v>0</v>
@@ -45777,7 +46052,7 @@
         <v>0</v>
       </c>
       <c r="AY149" s="2" t="n">
-        <v>10171875</v>
+        <v>7586804.399999998</v>
       </c>
       <c r="AZ149" t="n">
         <v>0</v>
@@ -45789,10 +46064,10 @@
         <v>0</v>
       </c>
       <c r="BD149" s="2" t="n">
-        <v>1287500</v>
+        <v>732799.9999999998</v>
       </c>
       <c r="BE149" s="2" t="n">
-        <v>1450625</v>
+        <v>783043.9999999998</v>
       </c>
       <c r="BF149" t="n">
         <v>0</v>
@@ -45811,43 +46086,43 @@
       </c>
       <c r="BK149" s="4" t="inlineStr"/>
       <c r="BL149" t="n">
-        <v>396875</v>
+        <v>83739.99999999999</v>
       </c>
       <c r="BM149" t="n">
-        <v>952500</v>
+        <v>200976</v>
       </c>
       <c r="BN149" t="n">
-        <v>238125</v>
+        <v>50243.99999999999</v>
       </c>
       <c r="BO149" t="n">
-        <v>271875</v>
+        <v>83739.99999999999</v>
       </c>
       <c r="BP149" t="n">
         <v>0</v>
       </c>
       <c r="BQ149" t="n">
-        <v>271875</v>
+        <v>83739.99999999999</v>
       </c>
       <c r="BR149" t="n">
-        <v>652500</v>
+        <v>200976</v>
       </c>
       <c r="BS149" t="n">
-        <v>163125</v>
+        <v>50243.99999999999</v>
       </c>
       <c r="BT149" s="2" t="n">
-        <v>652500</v>
+        <v>200976</v>
       </c>
       <c r="BU149" s="2" t="n">
-        <v>952500</v>
+        <v>200976</v>
       </c>
       <c r="BV149" s="2" t="n">
-        <v>19047500</v>
+        <v>19799024</v>
       </c>
       <c r="BW149" s="2" t="b">
         <v>0</v>
       </c>
       <c r="BX149" s="2" t="n">
-        <v>13336875</v>
+        <v>8369848.399999998</v>
       </c>
       <c r="BY149" s="2" t="b">
         <v>0</v>
@@ -45862,7 +46137,7 @@
         <v>0</v>
       </c>
       <c r="CC149" s="2" t="n">
-        <v>19047500</v>
+        <v>19799024</v>
       </c>
       <c r="CD149" t="n">
         <v>0</v>
@@ -45880,7 +46155,7 @@
         <v>0</v>
       </c>
       <c r="CI149" s="2" t="n">
-        <v>19047500</v>
+        <v>19799024</v>
       </c>
       <c r="CJ149" s="2" t="n">
         <v>0</v>
@@ -45901,13 +46176,13 @@
         <v>0</v>
       </c>
       <c r="CP149" s="2" t="n">
-        <v>18480000</v>
+        <v>7637348.399999998</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>jon_upside_case</t>
+          <t>jon_property_shock</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -45919,10 +46194,10 @@
         </is>
       </c>
       <c r="D150" s="2" t="n">
-        <v>6857500</v>
+        <v>-732500</v>
       </c>
       <c r="E150" t="n">
-        <v>26625375</v>
+        <v>18815782.5</v>
       </c>
       <c r="F150" t="n">
         <v>16000000</v>
@@ -45931,13 +46206,13 @@
         <v>2500000</v>
       </c>
       <c r="H150" t="n">
-        <v>8125375.000000004</v>
+        <v>315782.5</v>
       </c>
       <c r="I150" s="4" t="n">
-        <v>0.3791469194312796</v>
+        <v>0</v>
       </c>
       <c r="J150" s="2" t="n">
-        <v>2600000</v>
+        <v>2150000</v>
       </c>
       <c r="K150" s="2" t="n">
         <v>0</v>
@@ -45946,34 +46221,34 @@
         <v>1200000</v>
       </c>
       <c r="M150" t="n">
-        <v>215000</v>
+        <v>236000</v>
       </c>
       <c r="N150" t="n">
-        <v>2.166666666666667</v>
+        <v>1.791666666666667</v>
       </c>
       <c r="O150" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P150" s="2" t="n">
-        <v>2598196.0625</v>
+        <v>0</v>
       </c>
       <c r="Q150" t="n">
-        <v>18637762.5</v>
+        <v>13171047.75</v>
       </c>
       <c r="R150" t="n">
-        <v>2637762.5</v>
+        <v>-2828952.25</v>
       </c>
       <c r="S150" t="n">
-        <v>39566.4375</v>
+        <v>0</v>
       </c>
       <c r="T150" t="n">
-        <v>2598196.0625</v>
+        <v>0</v>
       </c>
       <c r="U150" t="n">
-        <v>2598196.0625</v>
+        <v>0</v>
       </c>
       <c r="V150" s="2" t="n">
-        <v>1185000</v>
+        <v>714000</v>
       </c>
       <c r="W150" s="2" t="n">
         <v>0</v>
@@ -45985,7 +46260,7 @@
         <v>0</v>
       </c>
       <c r="Z150" t="n">
-        <v>1450625</v>
+        <v>783043.9999999998</v>
       </c>
       <c r="AA150" t="n">
         <v>0</v>
@@ -46009,37 +46284,37 @@
         <v>0</v>
       </c>
       <c r="AH150" t="n">
-        <v>1450625</v>
+        <v>783043.9999999998</v>
       </c>
       <c r="AJ150" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AK150" s="2" t="n">
-        <v>1185000</v>
+        <v>714000</v>
       </c>
       <c r="AL150" s="4" t="n">
-        <v>1185000</v>
+        <v>714000</v>
       </c>
       <c r="AM150" s="2" t="n">
-        <v>711000</v>
+        <v>428400</v>
       </c>
       <c r="AN150" s="2" t="n">
-        <v>296250</v>
+        <v>178500</v>
       </c>
       <c r="AO150" s="2" t="n">
-        <v>177750</v>
+        <v>107100</v>
       </c>
       <c r="AP150" s="4" t="n">
-        <v>0.1848888078745905</v>
+        <v>0</v>
       </c>
       <c r="AQ150" s="2" t="n">
-        <v>8125375.000000004</v>
+        <v>315782.5</v>
       </c>
       <c r="AR150" s="2" t="n">
-        <v>10171875</v>
+        <v>7586804.399999998</v>
       </c>
       <c r="AS150" s="4" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="AT150" t="n">
         <v>0</v>
@@ -46057,30 +46332,25 @@
         <v>0</v>
       </c>
       <c r="AY150" s="2" t="n">
-        <v>11993906.25</v>
+        <v>8751588.971999997</v>
       </c>
       <c r="AZ150" t="n">
-        <v>2598196.0625</v>
-      </c>
-      <c r="BA150" t="inlineStr">
-        <is>
-          <t>deal:jon_deal_1:fund_liquidity</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="BB150" t="n">
-        <v>2598196.0625</v>
+        <v>0</v>
       </c>
       <c r="BC150" s="2" t="n">
-        <v>2598196.0625</v>
+        <v>0</v>
       </c>
       <c r="BD150" s="2" t="n">
-        <v>1450625</v>
+        <v>783043.9999999998</v>
       </c>
       <c r="BE150" s="2" t="n">
-        <v>1628375</v>
+        <v>890143.9999999998</v>
       </c>
       <c r="BF150" t="n">
-        <v>2598196.0625</v>
+        <v>0</v>
       </c>
       <c r="BG150" s="4" t="n">
         <v>0</v>
@@ -46096,58 +46366,58 @@
       </c>
       <c r="BK150" s="4" t="inlineStr"/>
       <c r="BL150" t="n">
-        <v>693125</v>
+        <v>262240</v>
       </c>
       <c r="BM150" t="n">
-        <v>1663500</v>
+        <v>629376</v>
       </c>
       <c r="BN150" t="n">
-        <v>415875</v>
+        <v>157344</v>
       </c>
       <c r="BO150" t="n">
-        <v>296250</v>
+        <v>178500</v>
       </c>
       <c r="BP150" t="n">
         <v>0</v>
       </c>
       <c r="BQ150" t="n">
-        <v>296250</v>
+        <v>178500</v>
       </c>
       <c r="BR150" t="n">
-        <v>711000</v>
+        <v>428400</v>
       </c>
       <c r="BS150" t="n">
-        <v>177750</v>
+        <v>107100</v>
       </c>
       <c r="BT150" s="2" t="n">
-        <v>711000</v>
+        <v>428400</v>
       </c>
       <c r="BU150" s="2" t="n">
-        <v>1663500</v>
+        <v>629376</v>
       </c>
       <c r="BV150" s="2" t="n">
-        <v>18336500</v>
+        <v>19370624</v>
       </c>
       <c r="BW150" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BX150" s="2" t="n">
-        <v>16220477.3125</v>
+        <v>9720678.596999997</v>
       </c>
       <c r="BY150" s="2" t="b">
         <v>0</v>
       </c>
       <c r="BZ150" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CA150" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CB150" s="2" t="b">
         <v>0</v>
       </c>
       <c r="CC150" s="2" t="n">
-        <v>18336500</v>
+        <v>19370624</v>
       </c>
       <c r="CD150" t="n">
         <v>0</v>
@@ -46165,7 +46435,7 @@
         <v>0</v>
       </c>
       <c r="CI150" s="2" t="n">
-        <v>5114499.25</v>
+        <v>19370624</v>
       </c>
       <c r="CJ150" s="2" t="n">
         <v>0</v>
@@ -46186,18 +46456,13 @@
         <v>0</v>
       </c>
       <c r="CP150" s="2" t="n">
-        <v>21747656.25</v>
-      </c>
-      <c r="CQ150" t="inlineStr">
-        <is>
-          <t>HURDLE_TRIGGER_ATTEMPTED_BUT_INSUFFICIENT</t>
-        </is>
+        <v>9957515.471999997</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>jon_upside_case</t>
+          <t>jon_property_shock</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -46209,10 +46474,10 @@
         </is>
       </c>
       <c r="D151" s="2" t="n">
-        <v>8125375.000000004</v>
+        <v>315782.5</v>
       </c>
       <c r="E151" t="n">
-        <v>27956643.75</v>
+        <v>19925913.6675</v>
       </c>
       <c r="F151" t="n">
         <v>16000000</v>
@@ -46221,13 +46486,13 @@
         <v>2500000</v>
       </c>
       <c r="H151" t="n">
-        <v>9456643.750000004</v>
+        <v>1425913.6675</v>
       </c>
       <c r="I151" s="4" t="n">
-        <v>0.3327846407088902</v>
+        <v>7.012738197968538</v>
       </c>
       <c r="J151" s="2" t="n">
-        <v>2704000</v>
+        <v>2214500</v>
       </c>
       <c r="K151" s="2" t="n">
         <v>0</v>
@@ -46236,34 +46501,34 @@
         <v>1200000</v>
       </c>
       <c r="M151" t="n">
-        <v>67600.00000000001</v>
+        <v>88580</v>
       </c>
       <c r="N151" t="n">
-        <v>2.253333333333334</v>
+        <v>1.845416666666667</v>
       </c>
       <c r="O151" s="2" t="n">
-        <v>2598196.0625</v>
+        <v>0</v>
       </c>
       <c r="P151" s="2" t="n">
-        <v>2598196.0625</v>
+        <v>0</v>
       </c>
       <c r="Q151" t="n">
-        <v>19569650.625</v>
+        <v>13948139.56725</v>
       </c>
       <c r="R151" t="n">
-        <v>971454.5625</v>
+        <v>-2051860.43275</v>
       </c>
       <c r="S151" t="n">
-        <v>14571.8184375</v>
+        <v>0</v>
       </c>
       <c r="T151" t="n">
-        <v>956882.7440625</v>
+        <v>0</v>
       </c>
       <c r="U151" t="n">
         <v>0</v>
       </c>
       <c r="V151" s="2" t="n">
-        <v>1436400</v>
+        <v>925920</v>
       </c>
       <c r="W151" s="2" t="n">
         <v>0</v>
@@ -46272,10 +46537,10 @@
         <v>1</v>
       </c>
       <c r="Y151" t="n">
-        <v>2598196.0625</v>
+        <v>0</v>
       </c>
       <c r="Z151" t="n">
-        <v>1628375</v>
+        <v>890143.9999999998</v>
       </c>
       <c r="AA151" t="n">
         <v>0</v>
@@ -46296,40 +46561,40 @@
         <v>0</v>
       </c>
       <c r="AG151" t="n">
-        <v>2598196.0625</v>
+        <v>0</v>
       </c>
       <c r="AH151" t="n">
-        <v>1628375</v>
+        <v>890143.9999999998</v>
       </c>
       <c r="AJ151" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AK151" s="2" t="n">
-        <v>1436400</v>
+        <v>925920</v>
       </c>
       <c r="AL151" s="4" t="n">
-        <v>1436400</v>
+        <v>925920</v>
       </c>
       <c r="AM151" s="2" t="n">
-        <v>861840.0000000002</v>
+        <v>555552</v>
       </c>
       <c r="AN151" s="2" t="n">
-        <v>359100.0000000001</v>
+        <v>231480</v>
       </c>
       <c r="AO151" s="2" t="n">
-        <v>215460.0000000001</v>
+        <v>138888</v>
       </c>
       <c r="AP151" s="4" t="n">
-        <v>0.1638408996507852</v>
+        <v>3.515492997553697</v>
       </c>
       <c r="AQ151" s="2" t="n">
-        <v>9456643.750000004</v>
+        <v>1425913.6675</v>
       </c>
       <c r="AR151" s="2" t="n">
-        <v>11993906.25</v>
+        <v>8751588.971999997</v>
       </c>
       <c r="AS151" s="4" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="AT151" t="n">
         <v>0</v>
@@ -46347,25 +46612,25 @@
         <v>0</v>
       </c>
       <c r="AY151" s="2" t="n">
-        <v>14152092.1875</v>
+        <v>10120775.53836</v>
       </c>
       <c r="AZ151" t="n">
         <v>0</v>
       </c>
       <c r="BB151" t="n">
-        <v>2598196.0625</v>
+        <v>0</v>
       </c>
       <c r="BC151" s="2" t="n">
-        <v>2598196.0625</v>
+        <v>0</v>
       </c>
       <c r="BD151" s="2" t="n">
-        <v>1628375</v>
+        <v>890143.9999999998</v>
       </c>
       <c r="BE151" s="2" t="n">
-        <v>1843835</v>
+        <v>1029032</v>
       </c>
       <c r="BF151" t="n">
-        <v>2598196.0625</v>
+        <v>0</v>
       </c>
       <c r="BG151" s="4" t="n">
         <v>0</v>
@@ -46381,58 +46646,58 @@
       </c>
       <c r="BK151" s="4" t="inlineStr"/>
       <c r="BL151" t="n">
-        <v>1052225</v>
+        <v>493720</v>
       </c>
       <c r="BM151" t="n">
-        <v>2525340</v>
+        <v>1184928</v>
       </c>
       <c r="BN151" t="n">
-        <v>631335</v>
+        <v>296232</v>
       </c>
       <c r="BO151" t="n">
-        <v>359100.0000000001</v>
+        <v>231480</v>
       </c>
       <c r="BP151" t="n">
         <v>0</v>
       </c>
       <c r="BQ151" t="n">
-        <v>359100.0000000001</v>
+        <v>231480</v>
       </c>
       <c r="BR151" t="n">
-        <v>861840.0000000002</v>
+        <v>555552</v>
       </c>
       <c r="BS151" t="n">
-        <v>215460.0000000001</v>
+        <v>138888</v>
       </c>
       <c r="BT151" s="2" t="n">
-        <v>861840.0000000002</v>
+        <v>555552</v>
       </c>
       <c r="BU151" s="2" t="n">
-        <v>2525340</v>
+        <v>1184928</v>
       </c>
       <c r="BV151" s="2" t="n">
-        <v>17474660</v>
+        <v>18815072</v>
       </c>
       <c r="BW151" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BX151" s="2" t="n">
-        <v>18594123.25</v>
+        <v>11506285.955235</v>
       </c>
       <c r="BY151" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BZ151" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CA151" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CB151" s="2" t="b">
         <v>0</v>
       </c>
       <c r="CC151" s="2" t="n">
-        <v>17474660</v>
+        <v>18815072</v>
       </c>
       <c r="CD151" t="n">
         <v>0</v>
@@ -46450,7 +46715,7 @@
         <v>0</v>
       </c>
       <c r="CI151" s="2" t="n">
-        <v>5244953.59375</v>
+        <v>18815072</v>
       </c>
       <c r="CJ151" s="2" t="n">
         <v>0</v>
@@ -46471,18 +46736,13 @@
         <v>0</v>
       </c>
       <c r="CP151" s="2" t="n">
-        <v>25452570.9375</v>
-      </c>
-      <c r="CQ151" t="inlineStr">
-        <is>
-          <t>HURDLE_TRIGGER_ATTEMPTED_BUT_INSUFFICIENT</t>
-        </is>
+        <v>12575721.20586</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>jon_upside_case</t>
+          <t>jon_property_shock</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -46494,10 +46754,10 @@
         </is>
       </c>
       <c r="D152" s="2" t="n">
-        <v>9456643.750000004</v>
+        <v>1425913.6675</v>
       </c>
       <c r="E152" t="n">
-        <v>29354475.93750001</v>
+        <v>21101542.5738825</v>
       </c>
       <c r="F152" t="n">
         <v>16000000</v>
@@ -46506,13 +46766,13 @@
         <v>2500000</v>
       </c>
       <c r="H152" t="n">
-        <v>10854475.93750001</v>
+        <v>2601542.573882498</v>
       </c>
       <c r="I152" s="4" t="n">
-        <v>0.2973740022722119</v>
+        <v>1.599630504979362</v>
       </c>
       <c r="J152" s="2" t="n">
-        <v>2812160</v>
+        <v>2280935</v>
       </c>
       <c r="K152" s="2" t="n">
         <v>0</v>
@@ -46521,34 +46781,34 @@
         <v>1200000</v>
       </c>
       <c r="M152" t="n">
-        <v>70304</v>
+        <v>91237.40000000001</v>
       </c>
       <c r="N152" t="n">
-        <v>2.343466666666667</v>
+        <v>1.900779166666667</v>
       </c>
       <c r="O152" s="2" t="n">
-        <v>2598196.0625</v>
+        <v>0</v>
       </c>
       <c r="P152" s="2" t="n">
-        <v>2598196.0625</v>
+        <v>0</v>
       </c>
       <c r="Q152" t="n">
-        <v>20548133.15625</v>
+        <v>14771079.80171775</v>
       </c>
       <c r="R152" t="n">
-        <v>1949937.093750004</v>
+        <v>-1228920.198282253</v>
       </c>
       <c r="S152" t="n">
-        <v>29249.05640625006</v>
+        <v>0</v>
       </c>
       <c r="T152" t="n">
-        <v>1920688.037343754</v>
+        <v>0</v>
       </c>
       <c r="U152" t="n">
         <v>0</v>
       </c>
       <c r="V152" s="2" t="n">
-        <v>1541856</v>
+        <v>989697.6</v>
       </c>
       <c r="W152" s="2" t="n">
         <v>0</v>
@@ -46557,10 +46817,10 @@
         <v>1</v>
       </c>
       <c r="Y152" t="n">
-        <v>2598196.0625</v>
+        <v>0</v>
       </c>
       <c r="Z152" t="n">
-        <v>1843835</v>
+        <v>1029032</v>
       </c>
       <c r="AA152" t="n">
         <v>0</v>
@@ -46581,40 +46841,40 @@
         <v>0</v>
       </c>
       <c r="AG152" t="n">
-        <v>2598196.0625</v>
+        <v>0</v>
       </c>
       <c r="AH152" t="n">
-        <v>1843835</v>
+        <v>1029032</v>
       </c>
       <c r="AJ152" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AK152" s="2" t="n">
-        <v>1541856</v>
+        <v>989697.6</v>
       </c>
       <c r="AL152" s="4" t="n">
-        <v>1541856</v>
+        <v>989697.6</v>
       </c>
       <c r="AM152" s="2" t="n">
-        <v>925113.6</v>
+        <v>593818.5599999999</v>
       </c>
       <c r="AN152" s="2" t="n">
-        <v>385464</v>
+        <v>247424.4</v>
       </c>
       <c r="AO152" s="2" t="n">
-        <v>231278.4</v>
+        <v>148454.64</v>
       </c>
       <c r="AP152" s="4" t="n">
-        <v>0.1478148299178557</v>
+        <v>0.8244741131093036</v>
       </c>
       <c r="AQ152" s="2" t="n">
-        <v>10854475.93750001</v>
+        <v>2601542.573882498</v>
       </c>
       <c r="AR152" s="2" t="n">
-        <v>14152092.1875</v>
+        <v>10120775.53836</v>
       </c>
       <c r="AS152" s="4" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="AT152" t="n">
         <v>0</v>
@@ -46632,22 +46892,22 @@
         <v>0</v>
       </c>
       <c r="AY152" s="2" t="n">
-        <v>4784133.078124996</v>
+        <v>11683900.75834679</v>
       </c>
       <c r="AZ152" t="n">
         <v>0</v>
       </c>
       <c r="BB152" t="n">
-        <v>2598196.0625</v>
+        <v>0</v>
       </c>
       <c r="BC152" s="2" t="n">
-        <v>2598196.0625</v>
+        <v>0</v>
       </c>
       <c r="BD152" s="2" t="n">
-        <v>1843835</v>
+        <v>1029032</v>
       </c>
       <c r="BE152" s="2" t="n">
-        <v>0</v>
+        <v>1177486.64</v>
       </c>
       <c r="BF152" t="n">
         <v>0</v>
@@ -46666,99 +46926,2654 @@
       </c>
       <c r="BK152" s="4" t="inlineStr"/>
       <c r="BL152" t="n">
+        <v>741144.4</v>
+      </c>
+      <c r="BM152" t="n">
+        <v>1778746.56</v>
+      </c>
+      <c r="BN152" t="n">
+        <v>444686.64</v>
+      </c>
+      <c r="BO152" t="n">
+        <v>247424.4</v>
+      </c>
+      <c r="BP152" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ152" t="n">
+        <v>247424.4</v>
+      </c>
+      <c r="BR152" t="n">
+        <v>593818.5599999999</v>
+      </c>
+      <c r="BS152" t="n">
+        <v>148454.64</v>
+      </c>
+      <c r="BT152" s="2" t="n">
+        <v>593818.5599999999</v>
+      </c>
+      <c r="BU152" s="2" t="n">
+        <v>1778746.56</v>
+      </c>
+      <c r="BV152" s="2" t="n">
+        <v>18221253.44</v>
+      </c>
+      <c r="BW152" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BX152" s="2" t="n">
+        <v>13511773.04181742</v>
+      </c>
+      <c r="BY152" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BZ152" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CA152" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CB152" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CC152" s="2" t="n">
+        <v>18221253.44</v>
+      </c>
+      <c r="CD152" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE152" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF152" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG152" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH152" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI152" s="2" t="n">
+        <v>18221253.44</v>
+      </c>
+      <c r="CJ152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP152" s="2" t="n">
+        <v>15462929.97222929</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>jon_property_shock</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>7</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>bottom_up</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="n">
+        <v>2601542.573882498</v>
+      </c>
+      <c r="E153" t="n">
+        <v>22346533.58574156</v>
+      </c>
+      <c r="F153" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="G153" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="H153" t="n">
+        <v>3846533.585741565</v>
+      </c>
+      <c r="I153" s="4" t="n">
+        <v>0.9030653865079172</v>
+      </c>
+      <c r="J153" s="2" t="n">
+        <v>2349363.05</v>
+      </c>
+      <c r="K153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L153" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="M153" t="n">
+        <v>93974.522</v>
+      </c>
+      <c r="N153" t="n">
+        <v>1.957802541666666</v>
+      </c>
+      <c r="O153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>15642573.51001909</v>
+      </c>
+      <c r="R153" t="n">
+        <v>-357426.4899809062</v>
+      </c>
+      <c r="S153" t="n">
+        <v>0</v>
+      </c>
+      <c r="T153" t="n">
+        <v>0</v>
+      </c>
+      <c r="U153" t="n">
+        <v>0</v>
+      </c>
+      <c r="V153" s="2" t="n">
+        <v>1055388.528</v>
+      </c>
+      <c r="W153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X153" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y153" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z153" t="n">
+        <v>1177486.64</v>
+      </c>
+      <c r="AA153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH153" t="n">
+        <v>1177486.64</v>
+      </c>
+      <c r="AJ153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK153" s="2" t="n">
+        <v>1055388.528</v>
+      </c>
+      <c r="AL153" s="4" t="n">
+        <v>1055388.528</v>
+      </c>
+      <c r="AM153" s="2" t="n">
+        <v>633233.1168</v>
+      </c>
+      <c r="AN153" s="2" t="n">
+        <v>263847.132</v>
+      </c>
+      <c r="AO153" s="2" t="n">
+        <v>158308.2792</v>
+      </c>
+      <c r="AP153" s="4" t="n">
+        <v>0.4785587690771722</v>
+      </c>
+      <c r="AQ153" s="2" t="n">
+        <v>3846533.585741565</v>
+      </c>
+      <c r="AR153" s="2" t="n">
+        <v>11683900.75834679</v>
+      </c>
+      <c r="AS153" s="4" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AT153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU153" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY153" s="2" t="n">
+        <v>13466654.98893188</v>
+      </c>
+      <c r="AZ153" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB153" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD153" s="2" t="n">
+        <v>1177486.64</v>
+      </c>
+      <c r="BE153" s="2" t="n">
+        <v>1335794.9192</v>
+      </c>
+      <c r="BF153" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG153" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH153" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI153" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ153" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK153" s="4" t="inlineStr"/>
+      <c r="BL153" t="n">
+        <v>1004991.532</v>
+      </c>
+      <c r="BM153" t="n">
+        <v>2411979.6768</v>
+      </c>
+      <c r="BN153" t="n">
+        <v>602994.9192</v>
+      </c>
+      <c r="BO153" t="n">
+        <v>263847.132</v>
+      </c>
+      <c r="BP153" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ153" t="n">
+        <v>263847.132</v>
+      </c>
+      <c r="BR153" t="n">
+        <v>633233.1168</v>
+      </c>
+      <c r="BS153" t="n">
+        <v>158308.2792</v>
+      </c>
+      <c r="BT153" s="2" t="n">
+        <v>633233.1168</v>
+      </c>
+      <c r="BU153" s="2" t="n">
+        <v>2411979.6768</v>
+      </c>
+      <c r="BV153" s="2" t="n">
+        <v>17588020.3232</v>
+      </c>
+      <c r="BW153" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BX153" s="2" t="n">
+        <v>15764083.30456727</v>
+      </c>
+      <c r="BY153" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BZ153" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CA153" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CB153" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CC153" s="2" t="n">
+        <v>17588020.3232</v>
+      </c>
+      <c r="CD153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI153" s="2" t="n">
+        <v>8172611.154524514</v>
+      </c>
+      <c r="CJ153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP153" s="2" t="n">
+        <v>18648983.49387344</v>
+      </c>
+      <c r="CQ153" t="inlineStr">
+        <is>
+          <t>HURDLE_TRIGGER_ATTEMPTED_BUT_INSUFFICIENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>jon_property_shock</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>8</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>bottom_up</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="n">
+        <v>3846533.585741565</v>
+      </c>
+      <c r="E154" t="n">
+        <v>23664979.06730032</v>
+      </c>
+      <c r="F154" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="G154" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="H154" t="n">
+        <v>5164979.067300316</v>
+      </c>
+      <c r="I154" s="4" t="n">
+        <v>0.6290973125699314</v>
+      </c>
+      <c r="J154" s="2" t="n">
+        <v>2419843.9415</v>
+      </c>
+      <c r="K154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L154" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="M154" t="n">
+        <v>96793.75766</v>
+      </c>
+      <c r="N154" t="n">
+        <v>2.016536617916667</v>
+      </c>
+      <c r="O154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>16565485.34711022</v>
+      </c>
+      <c r="R154" t="n">
+        <v>565485.3471102193</v>
+      </c>
+      <c r="S154" t="n">
+        <v>14137.13367775548</v>
+      </c>
+      <c r="T154" t="n">
+        <v>551348.2134324638</v>
+      </c>
+      <c r="U154" t="n">
+        <v>0</v>
+      </c>
+      <c r="V154" s="2" t="n">
+        <v>1123050.18384</v>
+      </c>
+      <c r="W154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X154" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y154" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z154" t="n">
+        <v>1335794.9192</v>
+      </c>
+      <c r="AA154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH154" t="n">
+        <v>1335794.9192</v>
+      </c>
+      <c r="AJ154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK154" s="2" t="n">
+        <v>1123050.18384</v>
+      </c>
+      <c r="AL154" s="4" t="n">
+        <v>1123050.18384</v>
+      </c>
+      <c r="AM154" s="2" t="n">
+        <v>673830.110304</v>
+      </c>
+      <c r="AN154" s="2" t="n">
+        <v>280762.54596</v>
+      </c>
+      <c r="AO154" s="2" t="n">
+        <v>168457.527576</v>
+      </c>
+      <c r="AP154" s="4" t="n">
+        <v>0.3427619835287545</v>
+      </c>
+      <c r="AQ154" s="2" t="n">
+        <v>5164979.067300316</v>
+      </c>
+      <c r="AR154" s="2" t="n">
+        <v>13466654.98893188</v>
+      </c>
+      <c r="AS154" s="4" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AT154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU154" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY154" s="2" t="n">
+        <v>15498082.68345302</v>
+      </c>
+      <c r="AZ154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD154" s="2" t="n">
+        <v>1335794.9192</v>
+      </c>
+      <c r="BE154" s="2" t="n">
+        <v>1504252.446776</v>
+      </c>
+      <c r="BF154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG154" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH154" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI154" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ154" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK154" s="4" t="inlineStr"/>
+      <c r="BL154" t="n">
+        <v>1285754.07796</v>
+      </c>
+      <c r="BM154" t="n">
+        <v>3085809.787104</v>
+      </c>
+      <c r="BN154" t="n">
+        <v>771452.446776</v>
+      </c>
+      <c r="BO154" t="n">
+        <v>280762.54596</v>
+      </c>
+      <c r="BP154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ154" t="n">
+        <v>280762.54596</v>
+      </c>
+      <c r="BR154" t="n">
+        <v>673830.110304</v>
+      </c>
+      <c r="BS154" t="n">
+        <v>168457.527576</v>
+      </c>
+      <c r="BT154" s="2" t="n">
+        <v>673830.110304</v>
+      </c>
+      <c r="BU154" s="2" t="n">
+        <v>3085809.787104</v>
+      </c>
+      <c r="BV154" s="2" t="n">
+        <v>16914190.212896</v>
+      </c>
+      <c r="BW154" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BX154" s="2" t="n">
+        <v>18293579.8970541</v>
+      </c>
+      <c r="BY154" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BZ154" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CA154" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CB154" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CC154" s="2" t="n">
+        <v>16914190.212896</v>
+      </c>
+      <c r="CD154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI154" s="2" t="n">
+        <v>2495130.986705158</v>
+      </c>
+      <c r="CJ154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP154" s="2" t="n">
+        <v>22167314.19752933</v>
+      </c>
+      <c r="CQ154" t="inlineStr">
+        <is>
+          <t>HURDLE_TRIGGER_ATTEMPTED_BUT_INSUFFICIENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>jon_property_shock</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>9</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>bottom_up</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="n">
+        <v>5164979.067300316</v>
+      </c>
+      <c r="E155" t="n">
+        <v>24374928.43931933</v>
+      </c>
+      <c r="F155" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="G155" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="H155" t="n">
+        <v>5874928.439319327</v>
+      </c>
+      <c r="I155" s="4" t="n">
+        <v>0.4825652199686016</v>
+      </c>
+      <c r="J155" s="2" t="n">
+        <v>2492439.259745</v>
+      </c>
+      <c r="K155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L155" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="M155" t="n">
+        <v>99697.57038980001</v>
+      </c>
+      <c r="N155" t="n">
+        <v>2.077032716454167</v>
+      </c>
+      <c r="O155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>17062449.90752353</v>
+      </c>
+      <c r="R155" t="n">
+        <v>1062449.907523528</v>
+      </c>
+      <c r="S155" t="n">
+        <v>26561.24768808819</v>
+      </c>
+      <c r="T155" t="n">
+        <v>1035888.65983544</v>
+      </c>
+      <c r="U155" t="n">
+        <v>0</v>
+      </c>
+      <c r="V155" s="2" t="n">
+        <v>1192741.6893552</v>
+      </c>
+      <c r="W155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X155" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y155" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z155" t="n">
+        <v>1504252.446776</v>
+      </c>
+      <c r="AA155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH155" t="n">
+        <v>1504252.446776</v>
+      </c>
+      <c r="AJ155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK155" s="2" t="n">
+        <v>1192741.6893552</v>
+      </c>
+      <c r="AL155" s="4" t="n">
+        <v>1192741.6893552</v>
+      </c>
+      <c r="AM155" s="2" t="n">
+        <v>715645.01361312</v>
+      </c>
+      <c r="AN155" s="2" t="n">
+        <v>298185.4223388</v>
+      </c>
+      <c r="AO155" s="2" t="n">
+        <v>178911.25340328</v>
+      </c>
+      <c r="AP155" s="4" t="n">
+        <v>0.1374544529161268</v>
+      </c>
+      <c r="AQ155" s="2" t="n">
+        <v>5874928.439319327</v>
+      </c>
+      <c r="AR155" s="2" t="n">
+        <v>15498082.68345302</v>
+      </c>
+      <c r="AS155" s="4" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AT155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU155" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY155" s="2" t="n">
+        <v>4452754.713660177</v>
+      </c>
+      <c r="AZ155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC155" s="2" t="n">
+        <v>1157117.358123071</v>
+      </c>
+      <c r="BD155" s="2" t="n">
+        <v>1504252.446776</v>
+      </c>
+      <c r="BE155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG155" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH155" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI155" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ155" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK155" s="4" t="inlineStr"/>
+      <c r="BL155" t="n">
+        <v>1583939.5002988</v>
+      </c>
+      <c r="BM155" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="BN155" t="n">
+        <v>950363.70017928</v>
+      </c>
+      <c r="BO155" t="n">
+        <v>298185.4223388</v>
+      </c>
+      <c r="BP155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ155" t="n">
+        <v>298185.4223388</v>
+      </c>
+      <c r="BR155" t="n">
+        <v>16914190.212896</v>
+      </c>
+      <c r="BS155" t="n">
+        <v>178911.25340328</v>
+      </c>
+      <c r="BT155" s="2" t="n">
+        <v>16914190.212896</v>
+      </c>
+      <c r="BU155" s="2" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="BV155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW155" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BX155" s="2" t="n">
+        <v>20962914.66464982</v>
+      </c>
+      <c r="BY155" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BZ155" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CA155" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CB155" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CC155" s="2" t="n">
+        <v>16198545.19928288</v>
+      </c>
+      <c r="CD155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE155" t="n">
+        <v>1683163.70017928</v>
+      </c>
+      <c r="CF155" t="n">
+        <v>13358264.14098053</v>
+      </c>
+      <c r="CG155" t="n">
+        <v>1157117.358123071</v>
+      </c>
+      <c r="CH155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ155" s="2" t="n">
+        <v>13358264.14098053</v>
+      </c>
+      <c r="CK155" s="2" t="n">
+        <v>1157117.358123071</v>
+      </c>
+      <c r="CL155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO155" s="2" t="n">
+        <v>9170565.794856433</v>
+      </c>
+      <c r="CP155" s="2" t="n">
+        <v>9170565.794856433</v>
+      </c>
+      <c r="CQ155" t="inlineStr">
+        <is>
+          <t>HURDLE_COMPLETION_TRIGGER_EXECUTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>jon_upside_case</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>1</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>bottom_up</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="E156" t="n">
+        <v>23000000</v>
+      </c>
+      <c r="F156" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="G156" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="H156" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="I156" s="4" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="J156" s="2" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="K156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L156" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="M156" t="n">
+        <v>387500</v>
+      </c>
+      <c r="N156" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>16100000</v>
+      </c>
+      <c r="R156" t="n">
+        <v>99999.99999999814</v>
+      </c>
+      <c r="S156" t="n">
+        <v>1499.999999999972</v>
+      </c>
+      <c r="T156" t="n">
+        <v>98499.99999999817</v>
+      </c>
+      <c r="U156" t="n">
+        <v>0</v>
+      </c>
+      <c r="V156" s="2" t="n">
+        <v>-87500</v>
+      </c>
+      <c r="W156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X156" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y156" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z156" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="AA156" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="AB156" s="2" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="AC156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH156" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="AI156" t="inlineStr">
+        <is>
+          <t>initial_lp_capital</t>
+        </is>
+      </c>
+      <c r="AJ156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK156" s="2" t="n">
+        <v>-87500</v>
+      </c>
+      <c r="AL156" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP156" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ156" s="2" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="AR156" s="2" t="n">
+        <v>5200000</v>
+      </c>
+      <c r="AS156" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AT156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU156" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY156" s="2" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="AZ156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD156" s="2" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="BE156" s="2" t="n">
+        <v>1212500</v>
+      </c>
+      <c r="BF156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG156" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH156" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI156" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ156" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK156" s="4" t="inlineStr"/>
+      <c r="BL156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV156" s="2" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="BW156" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BX156" s="2" t="n">
+        <v>8837500</v>
+      </c>
+      <c r="BY156" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BZ156" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CA156" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CB156" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CC156" s="2" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="CD156" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE156" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF156" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG156" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH156" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI156" s="2" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="CJ156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP156" s="2" t="n">
+        <v>12212500</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>jon_upside_case</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>2</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>bottom_up</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="E157" t="n">
+        <v>24150000</v>
+      </c>
+      <c r="F157" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="G157" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="H157" t="n">
+        <v>5650000</v>
+      </c>
+      <c r="I157" s="4" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="J157" s="2" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="K157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L157" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="M157" t="n">
+        <v>300000</v>
+      </c>
+      <c r="N157" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="O157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>16905000</v>
+      </c>
+      <c r="R157" t="n">
+        <v>905000</v>
+      </c>
+      <c r="S157" t="n">
+        <v>13575</v>
+      </c>
+      <c r="T157" t="n">
+        <v>891425</v>
+      </c>
+      <c r="U157" t="n">
+        <v>0</v>
+      </c>
+      <c r="V157" s="2" t="n">
+        <v>500000</v>
+      </c>
+      <c r="W157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X157" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y157" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z157" t="n">
+        <v>1212500</v>
+      </c>
+      <c r="AA157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH157" t="n">
+        <v>1212500</v>
+      </c>
+      <c r="AJ157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK157" s="2" t="n">
+        <v>500000</v>
+      </c>
+      <c r="AL157" s="4" t="n">
+        <v>500000</v>
+      </c>
+      <c r="AM157" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="AN157" s="2" t="n">
+        <v>125000</v>
+      </c>
+      <c r="AO157" s="2" t="n">
+        <v>75000</v>
+      </c>
+      <c r="AP157" s="4" t="n">
+        <v>0.2555555555555555</v>
+      </c>
+      <c r="AQ157" s="2" t="n">
+        <v>5650000</v>
+      </c>
+      <c r="AR157" s="2" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="AS157" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AT157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU157" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY157" s="2" t="n">
+        <v>8250000</v>
+      </c>
+      <c r="AZ157" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB157" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD157" s="2" t="n">
+        <v>1212500</v>
+      </c>
+      <c r="BE157" s="2" t="n">
+        <v>1287500</v>
+      </c>
+      <c r="BF157" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG157" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH157" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI157" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ157" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK157" s="4" t="inlineStr"/>
+      <c r="BL157" t="n">
+        <v>125000</v>
+      </c>
+      <c r="BM157" t="n">
+        <v>300000</v>
+      </c>
+      <c r="BN157" t="n">
+        <v>75000</v>
+      </c>
+      <c r="BO157" t="n">
+        <v>125000</v>
+      </c>
+      <c r="BP157" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ157" t="n">
+        <v>125000</v>
+      </c>
+      <c r="BR157" t="n">
+        <v>300000</v>
+      </c>
+      <c r="BS157" t="n">
+        <v>75000</v>
+      </c>
+      <c r="BT157" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="BU157" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="BV157" s="2" t="n">
+        <v>19700000</v>
+      </c>
+      <c r="BW157" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BX157" s="2" t="n">
+        <v>10950000</v>
+      </c>
+      <c r="BY157" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BZ157" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CA157" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CB157" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CC157" s="2" t="n">
+        <v>19700000</v>
+      </c>
+      <c r="CD157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI157" s="2" t="n">
+        <v>19700000</v>
+      </c>
+      <c r="CJ157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP157" s="2" t="n">
+        <v>15187500</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>jon_upside_case</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>3</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>bottom_up</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="n">
+        <v>5650000</v>
+      </c>
+      <c r="E158" t="n">
+        <v>25357500</v>
+      </c>
+      <c r="F158" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="G158" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="H158" t="n">
+        <v>6857500</v>
+      </c>
+      <c r="I158" s="4" t="n">
+        <v>0.4424778761061947</v>
+      </c>
+      <c r="J158" s="2" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="K158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L158" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="M158" t="n">
+        <v>212500</v>
+      </c>
+      <c r="N158" t="n">
+        <v>2.083333333333333</v>
+      </c>
+      <c r="O158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>17750250</v>
+      </c>
+      <c r="R158" t="n">
+        <v>1750250</v>
+      </c>
+      <c r="S158" t="n">
+        <v>26253.75</v>
+      </c>
+      <c r="T158" t="n">
+        <v>1723996.25</v>
+      </c>
+      <c r="U158" t="n">
+        <v>0</v>
+      </c>
+      <c r="V158" s="2" t="n">
+        <v>1087500</v>
+      </c>
+      <c r="W158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X158" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y158" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z158" t="n">
+        <v>1287500</v>
+      </c>
+      <c r="AA158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH158" t="n">
+        <v>1287500</v>
+      </c>
+      <c r="AJ158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK158" s="2" t="n">
+        <v>1087500</v>
+      </c>
+      <c r="AL158" s="4" t="n">
+        <v>1087500</v>
+      </c>
+      <c r="AM158" s="2" t="n">
+        <v>652500</v>
+      </c>
+      <c r="AN158" s="2" t="n">
+        <v>271875</v>
+      </c>
+      <c r="AO158" s="2" t="n">
+        <v>163125</v>
+      </c>
+      <c r="AP158" s="4" t="n">
+        <v>0.213716814159292</v>
+      </c>
+      <c r="AQ158" s="2" t="n">
+        <v>6857500</v>
+      </c>
+      <c r="AR158" s="2" t="n">
+        <v>8250000</v>
+      </c>
+      <c r="AS158" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AT158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU158" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY158" s="2" t="n">
+        <v>10171875</v>
+      </c>
+      <c r="AZ158" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB158" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD158" s="2" t="n">
+        <v>1287500</v>
+      </c>
+      <c r="BE158" s="2" t="n">
+        <v>1450625</v>
+      </c>
+      <c r="BF158" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG158" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH158" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI158" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ158" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK158" s="4" t="inlineStr"/>
+      <c r="BL158" t="n">
+        <v>396875</v>
+      </c>
+      <c r="BM158" t="n">
+        <v>952500</v>
+      </c>
+      <c r="BN158" t="n">
+        <v>238125</v>
+      </c>
+      <c r="BO158" t="n">
+        <v>271875</v>
+      </c>
+      <c r="BP158" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ158" t="n">
+        <v>271875</v>
+      </c>
+      <c r="BR158" t="n">
+        <v>652500</v>
+      </c>
+      <c r="BS158" t="n">
+        <v>163125</v>
+      </c>
+      <c r="BT158" s="2" t="n">
+        <v>652500</v>
+      </c>
+      <c r="BU158" s="2" t="n">
+        <v>952500</v>
+      </c>
+      <c r="BV158" s="2" t="n">
+        <v>19047500</v>
+      </c>
+      <c r="BW158" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BX158" s="2" t="n">
+        <v>13336875</v>
+      </c>
+      <c r="BY158" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BZ158" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CA158" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CB158" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CC158" s="2" t="n">
+        <v>19047500</v>
+      </c>
+      <c r="CD158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI158" s="2" t="n">
+        <v>19047500</v>
+      </c>
+      <c r="CJ158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP158" s="2" t="n">
+        <v>18480000</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>jon_upside_case</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>4</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>bottom_up</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="n">
+        <v>6857500</v>
+      </c>
+      <c r="E159" t="n">
+        <v>26625375</v>
+      </c>
+      <c r="F159" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="G159" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="H159" t="n">
+        <v>8125375.000000004</v>
+      </c>
+      <c r="I159" s="4" t="n">
+        <v>0.3791469194312796</v>
+      </c>
+      <c r="J159" s="2" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="K159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L159" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="M159" t="n">
+        <v>215000</v>
+      </c>
+      <c r="N159" t="n">
+        <v>2.166666666666667</v>
+      </c>
+      <c r="O159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P159" s="2" t="n">
+        <v>2598196.0625</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>18637762.5</v>
+      </c>
+      <c r="R159" t="n">
+        <v>2637762.5</v>
+      </c>
+      <c r="S159" t="n">
+        <v>39566.4375</v>
+      </c>
+      <c r="T159" t="n">
+        <v>2598196.0625</v>
+      </c>
+      <c r="U159" t="n">
+        <v>2598196.0625</v>
+      </c>
+      <c r="V159" s="2" t="n">
+        <v>1185000</v>
+      </c>
+      <c r="W159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X159" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y159" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z159" t="n">
+        <v>1450625</v>
+      </c>
+      <c r="AA159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH159" t="n">
+        <v>1450625</v>
+      </c>
+      <c r="AJ159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK159" s="2" t="n">
+        <v>1185000</v>
+      </c>
+      <c r="AL159" s="4" t="n">
+        <v>1185000</v>
+      </c>
+      <c r="AM159" s="2" t="n">
+        <v>711000</v>
+      </c>
+      <c r="AN159" s="2" t="n">
+        <v>296250</v>
+      </c>
+      <c r="AO159" s="2" t="n">
+        <v>177750</v>
+      </c>
+      <c r="AP159" s="4" t="n">
+        <v>0.1848888078745905</v>
+      </c>
+      <c r="AQ159" s="2" t="n">
+        <v>8125375.000000004</v>
+      </c>
+      <c r="AR159" s="2" t="n">
+        <v>10171875</v>
+      </c>
+      <c r="AS159" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AT159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU159" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY159" s="2" t="n">
+        <v>11993906.25</v>
+      </c>
+      <c r="AZ159" t="n">
+        <v>2598196.0625</v>
+      </c>
+      <c r="BA159" t="inlineStr">
+        <is>
+          <t>deal:jon_deal_1:fund_liquidity</t>
+        </is>
+      </c>
+      <c r="BB159" t="n">
+        <v>2598196.0625</v>
+      </c>
+      <c r="BC159" s="2" t="n">
+        <v>2598196.0625</v>
+      </c>
+      <c r="BD159" s="2" t="n">
+        <v>1450625</v>
+      </c>
+      <c r="BE159" s="2" t="n">
+        <v>1628375</v>
+      </c>
+      <c r="BF159" t="n">
+        <v>2598196.0625</v>
+      </c>
+      <c r="BG159" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH159" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI159" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ159" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK159" s="4" t="inlineStr"/>
+      <c r="BL159" t="n">
+        <v>693125</v>
+      </c>
+      <c r="BM159" t="n">
+        <v>1663500</v>
+      </c>
+      <c r="BN159" t="n">
+        <v>415875</v>
+      </c>
+      <c r="BO159" t="n">
+        <v>296250</v>
+      </c>
+      <c r="BP159" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ159" t="n">
+        <v>296250</v>
+      </c>
+      <c r="BR159" t="n">
+        <v>711000</v>
+      </c>
+      <c r="BS159" t="n">
+        <v>177750</v>
+      </c>
+      <c r="BT159" s="2" t="n">
+        <v>711000</v>
+      </c>
+      <c r="BU159" s="2" t="n">
+        <v>1663500</v>
+      </c>
+      <c r="BV159" s="2" t="n">
+        <v>18336500</v>
+      </c>
+      <c r="BW159" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BX159" s="2" t="n">
+        <v>16220477.3125</v>
+      </c>
+      <c r="BY159" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BZ159" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CA159" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CB159" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CC159" s="2" t="n">
+        <v>18336500</v>
+      </c>
+      <c r="CD159" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE159" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF159" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG159" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH159" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI159" s="2" t="n">
+        <v>5114499.25</v>
+      </c>
+      <c r="CJ159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP159" s="2" t="n">
+        <v>21747656.25</v>
+      </c>
+      <c r="CQ159" t="inlineStr">
+        <is>
+          <t>HURDLE_TRIGGER_ATTEMPTED_BUT_INSUFFICIENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>jon_upside_case</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>5</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>bottom_up</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="n">
+        <v>8125375.000000004</v>
+      </c>
+      <c r="E160" t="n">
+        <v>27956643.75</v>
+      </c>
+      <c r="F160" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="G160" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="H160" t="n">
+        <v>9456643.750000004</v>
+      </c>
+      <c r="I160" s="4" t="n">
+        <v>0.3327846407088902</v>
+      </c>
+      <c r="J160" s="2" t="n">
+        <v>2704000</v>
+      </c>
+      <c r="K160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L160" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="M160" t="n">
+        <v>67600.00000000001</v>
+      </c>
+      <c r="N160" t="n">
+        <v>2.253333333333334</v>
+      </c>
+      <c r="O160" s="2" t="n">
+        <v>2598196.0625</v>
+      </c>
+      <c r="P160" s="2" t="n">
+        <v>2598196.0625</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>19569650.625</v>
+      </c>
+      <c r="R160" t="n">
+        <v>971454.5625</v>
+      </c>
+      <c r="S160" t="n">
+        <v>14571.8184375</v>
+      </c>
+      <c r="T160" t="n">
+        <v>956882.7440625</v>
+      </c>
+      <c r="U160" t="n">
+        <v>0</v>
+      </c>
+      <c r="V160" s="2" t="n">
+        <v>1436400</v>
+      </c>
+      <c r="W160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X160" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y160" t="n">
+        <v>2598196.0625</v>
+      </c>
+      <c r="Z160" t="n">
+        <v>1628375</v>
+      </c>
+      <c r="AA160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG160" t="n">
+        <v>2598196.0625</v>
+      </c>
+      <c r="AH160" t="n">
+        <v>1628375</v>
+      </c>
+      <c r="AJ160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK160" s="2" t="n">
+        <v>1436400</v>
+      </c>
+      <c r="AL160" s="4" t="n">
+        <v>1436400</v>
+      </c>
+      <c r="AM160" s="2" t="n">
+        <v>861840.0000000002</v>
+      </c>
+      <c r="AN160" s="2" t="n">
+        <v>359100.0000000001</v>
+      </c>
+      <c r="AO160" s="2" t="n">
+        <v>215460.0000000001</v>
+      </c>
+      <c r="AP160" s="4" t="n">
+        <v>0.1638408996507852</v>
+      </c>
+      <c r="AQ160" s="2" t="n">
+        <v>9456643.750000004</v>
+      </c>
+      <c r="AR160" s="2" t="n">
+        <v>11993906.25</v>
+      </c>
+      <c r="AS160" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AT160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU160" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY160" s="2" t="n">
+        <v>14152092.1875</v>
+      </c>
+      <c r="AZ160" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB160" t="n">
+        <v>2598196.0625</v>
+      </c>
+      <c r="BC160" s="2" t="n">
+        <v>2598196.0625</v>
+      </c>
+      <c r="BD160" s="2" t="n">
+        <v>1628375</v>
+      </c>
+      <c r="BE160" s="2" t="n">
+        <v>1843835</v>
+      </c>
+      <c r="BF160" t="n">
+        <v>2598196.0625</v>
+      </c>
+      <c r="BG160" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH160" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI160" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ160" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK160" s="4" t="inlineStr"/>
+      <c r="BL160" t="n">
+        <v>1052225</v>
+      </c>
+      <c r="BM160" t="n">
+        <v>2525340</v>
+      </c>
+      <c r="BN160" t="n">
+        <v>631335</v>
+      </c>
+      <c r="BO160" t="n">
+        <v>359100.0000000001</v>
+      </c>
+      <c r="BP160" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ160" t="n">
+        <v>359100.0000000001</v>
+      </c>
+      <c r="BR160" t="n">
+        <v>861840.0000000002</v>
+      </c>
+      <c r="BS160" t="n">
+        <v>215460.0000000001</v>
+      </c>
+      <c r="BT160" s="2" t="n">
+        <v>861840.0000000002</v>
+      </c>
+      <c r="BU160" s="2" t="n">
+        <v>2525340</v>
+      </c>
+      <c r="BV160" s="2" t="n">
+        <v>17474660</v>
+      </c>
+      <c r="BW160" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BX160" s="2" t="n">
+        <v>18594123.25</v>
+      </c>
+      <c r="BY160" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BZ160" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CA160" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CB160" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CC160" s="2" t="n">
+        <v>17474660</v>
+      </c>
+      <c r="CD160" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE160" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF160" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG160" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH160" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI160" s="2" t="n">
+        <v>5244953.59375</v>
+      </c>
+      <c r="CJ160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP160" s="2" t="n">
+        <v>25452570.9375</v>
+      </c>
+      <c r="CQ160" t="inlineStr">
+        <is>
+          <t>HURDLE_TRIGGER_ATTEMPTED_BUT_INSUFFICIENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>jon_upside_case</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>6</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>bottom_up</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="n">
+        <v>9456643.750000004</v>
+      </c>
+      <c r="E161" t="n">
+        <v>29354475.93750001</v>
+      </c>
+      <c r="F161" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="G161" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="H161" t="n">
+        <v>10854475.93750001</v>
+      </c>
+      <c r="I161" s="4" t="n">
+        <v>0.2973740022722119</v>
+      </c>
+      <c r="J161" s="2" t="n">
+        <v>2812160</v>
+      </c>
+      <c r="K161" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L161" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="M161" t="n">
+        <v>70304</v>
+      </c>
+      <c r="N161" t="n">
+        <v>2.343466666666667</v>
+      </c>
+      <c r="O161" s="2" t="n">
+        <v>2598196.0625</v>
+      </c>
+      <c r="P161" s="2" t="n">
+        <v>2598196.0625</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>20548133.15625</v>
+      </c>
+      <c r="R161" t="n">
+        <v>1949937.093750004</v>
+      </c>
+      <c r="S161" t="n">
+        <v>29249.05640625006</v>
+      </c>
+      <c r="T161" t="n">
+        <v>1920688.037343754</v>
+      </c>
+      <c r="U161" t="n">
+        <v>0</v>
+      </c>
+      <c r="V161" s="2" t="n">
+        <v>1541856</v>
+      </c>
+      <c r="W161" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X161" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y161" t="n">
+        <v>2598196.0625</v>
+      </c>
+      <c r="Z161" t="n">
+        <v>1843835</v>
+      </c>
+      <c r="AA161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB161" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG161" t="n">
+        <v>2598196.0625</v>
+      </c>
+      <c r="AH161" t="n">
+        <v>1843835</v>
+      </c>
+      <c r="AJ161" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK161" s="2" t="n">
+        <v>1541856</v>
+      </c>
+      <c r="AL161" s="4" t="n">
+        <v>1541856</v>
+      </c>
+      <c r="AM161" s="2" t="n">
+        <v>925113.6</v>
+      </c>
+      <c r="AN161" s="2" t="n">
+        <v>385464</v>
+      </c>
+      <c r="AO161" s="2" t="n">
+        <v>231278.4</v>
+      </c>
+      <c r="AP161" s="4" t="n">
+        <v>0.1478148299178557</v>
+      </c>
+      <c r="AQ161" s="2" t="n">
+        <v>10854475.93750001</v>
+      </c>
+      <c r="AR161" s="2" t="n">
+        <v>14152092.1875</v>
+      </c>
+      <c r="AS161" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AT161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU161" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY161" s="2" t="n">
+        <v>4784133.078124996</v>
+      </c>
+      <c r="AZ161" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB161" t="n">
+        <v>2598196.0625</v>
+      </c>
+      <c r="BC161" s="2" t="n">
+        <v>2598196.0625</v>
+      </c>
+      <c r="BD161" s="2" t="n">
+        <v>1843835</v>
+      </c>
+      <c r="BE161" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF161" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG161" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH161" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI161" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ161" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK161" s="4" t="inlineStr"/>
+      <c r="BL161" t="n">
         <v>1437689</v>
       </c>
-      <c r="BM152" t="n">
+      <c r="BM161" t="n">
         <v>20000000</v>
       </c>
-      <c r="BN152" t="n">
+      <c r="BN161" t="n">
         <v>862613.4</v>
       </c>
-      <c r="BO152" t="n">
+      <c r="BO161" t="n">
         <v>385464</v>
       </c>
-      <c r="BP152" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ152" t="n">
+      <c r="BP161" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ161" t="n">
         <v>385464</v>
       </c>
-      <c r="BR152" t="n">
+      <c r="BR161" t="n">
         <v>17474660</v>
       </c>
-      <c r="BS152" t="n">
+      <c r="BS161" t="n">
         <v>231278.4</v>
       </c>
-      <c r="BT152" s="2" t="n">
+      <c r="BT161" s="2" t="n">
         <v>17474660</v>
       </c>
-      <c r="BU152" s="2" t="n">
+      <c r="BU161" s="2" t="n">
         <v>20000000</v>
       </c>
-      <c r="BV152" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW152" s="2" t="b">
+      <c r="BV161" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW161" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="BX152" s="2" t="n">
+      <c r="BX161" s="2" t="n">
         <v>21449102.4</v>
       </c>
-      <c r="BY152" s="2" t="b">
+      <c r="BY161" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="BZ152" s="2" t="b">
+      <c r="BZ161" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="CA152" s="2" t="b">
+      <c r="CA161" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="CB152" s="2" t="b">
+      <c r="CB161" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="CC152" s="2" t="n">
+      <c r="CC161" s="2" t="n">
         <v>16549546.4</v>
       </c>
-      <c r="CD152" t="n">
+      <c r="CD161" t="n">
         <v>2598196.0625</v>
       </c>
-      <c r="CE152" t="n">
+      <c r="CE161" t="n">
         <v>2075113.4</v>
       </c>
-      <c r="CF152" t="n">
+      <c r="CF161" t="n">
         <v>11876236.9375</v>
       </c>
-      <c r="CG152" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH152" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI152" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ152" s="2" t="n">
+      <c r="CG161" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH161" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI161" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ161" s="2" t="n">
         <v>11876236.9375</v>
       </c>
-      <c r="CK152" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL152" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM152" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN152" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO152" s="2" t="n">
+      <c r="CK161" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL161" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM161" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN161" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO161" s="2" t="n">
         <v>13040412.953125</v>
       </c>
-      <c r="CP152" s="2" t="n">
+      <c r="CP161" s="2" t="n">
         <v>13040412.953125</v>
       </c>
-      <c r="CQ152" t="inlineStr">
+      <c r="CQ161" t="inlineStr">
         <is>
           <t>HURDLE_COMPLETION_TRIGGER_EXECUTED</t>
         </is>
@@ -46775,10 +49590,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD34"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -49611,7 +52426,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>jon_upside_case</t>
+          <t>jon_property_shock</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -49641,7 +52456,7 @@
         <v>4500000</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1500000</v>
+        <v>1278000</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -49650,13 +52465,13 @@
         <v>1200000</v>
       </c>
       <c r="M29" t="n">
-        <v>387500</v>
+        <v>551120</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-87500</v>
+        <v>-473120</v>
       </c>
       <c r="O29" t="n">
-        <v>1.25</v>
+        <v>1.065</v>
       </c>
       <c r="P29" s="2" t="n">
         <v>0</v>
@@ -49671,10 +52486,10 @@
         <v>99999.99999999814</v>
       </c>
       <c r="T29" t="n">
-        <v>1499.999999999972</v>
+        <v>2499.999999999954</v>
       </c>
       <c r="U29" t="n">
-        <v>98499.99999999817</v>
+        <v>97499.99999999818</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -49709,7 +52524,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>jon_upside_case</t>
+          <t>jon_property_shock</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -49727,7 +52542,7 @@
         <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>24150000</v>
+        <v>23690000</v>
       </c>
       <c r="G30" t="n">
         <v>16000000</v>
@@ -49736,10 +52551,10 @@
         <v>2500000</v>
       </c>
       <c r="I30" t="n">
-        <v>5650000</v>
+        <v>5190000</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>2000000</v>
+        <v>1568666.666666667</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -49748,13 +52563,13 @@
         <v>1200000</v>
       </c>
       <c r="M30" t="n">
-        <v>300000</v>
+        <v>462746.6666666667</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>500000</v>
+        <v>-94080.00000000017</v>
       </c>
       <c r="O30" t="n">
-        <v>1.666666666666667</v>
+        <v>1.307222222222222</v>
       </c>
       <c r="P30" s="2" t="n">
         <v>0</v>
@@ -49763,16 +52578,16 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>16905000</v>
+        <v>16583000</v>
       </c>
       <c r="S30" t="n">
-        <v>905000</v>
+        <v>582999.9999999981</v>
       </c>
       <c r="T30" t="n">
-        <v>13575</v>
+        <v>14574.99999999995</v>
       </c>
       <c r="U30" t="n">
-        <v>891425</v>
+        <v>568424.9999999981</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -49781,19 +52596,19 @@
         <v>0</v>
       </c>
       <c r="X30" s="2" t="n">
-        <v>5650000</v>
+        <v>5190000</v>
       </c>
       <c r="Y30" s="2" t="n">
-        <v>5650000</v>
+        <v>5190000</v>
       </c>
       <c r="Z30" s="2" t="n">
-        <v>5650000</v>
+        <v>5190000</v>
       </c>
       <c r="AA30" t="n">
         <v>1000000</v>
       </c>
       <c r="AB30" s="3" t="n">
-        <v>1.614285714285714</v>
+        <v>1.482857142857143</v>
       </c>
       <c r="AC30" t="n">
         <v>3500000</v>
@@ -49807,7 +52622,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>jon_upside_case</t>
+          <t>jon_property_shock</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -49825,7 +52640,7 @@
         <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>25357500</v>
+        <v>17767500</v>
       </c>
       <c r="G31" t="n">
         <v>16000000</v>
@@ -49834,10 +52649,10 @@
         <v>2500000</v>
       </c>
       <c r="I31" t="n">
-        <v>6857500</v>
+        <v>-732500</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>2500000</v>
+        <v>1859333.333333333</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -49846,13 +52661,13 @@
         <v>1200000</v>
       </c>
       <c r="M31" t="n">
-        <v>212500</v>
+        <v>324373.3333333333</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>1087500</v>
+        <v>334959.9999999999</v>
       </c>
       <c r="O31" t="n">
-        <v>2.083333333333333</v>
+        <v>1.549444444444444</v>
       </c>
       <c r="P31" s="2" t="n">
         <v>0</v>
@@ -49861,16 +52676,16 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>17750250</v>
+        <v>12437250</v>
       </c>
       <c r="S31" t="n">
-        <v>1750250</v>
+        <v>-3562750</v>
       </c>
       <c r="T31" t="n">
-        <v>26253.75</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1723996.25</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -49879,19 +52694,19 @@
         <v>0</v>
       </c>
       <c r="X31" s="2" t="n">
-        <v>6857500</v>
+        <v>-732500</v>
       </c>
       <c r="Y31" s="2" t="n">
-        <v>6857500</v>
+        <v>-732500</v>
       </c>
       <c r="Z31" s="2" t="n">
-        <v>6857500</v>
+        <v>-732500</v>
       </c>
       <c r="AA31" t="n">
         <v>1000000</v>
       </c>
       <c r="AB31" s="3" t="n">
-        <v>1.959285714285714</v>
+        <v>-0.2092857142857143</v>
       </c>
       <c r="AC31" t="n">
         <v>3500000</v>
@@ -49905,7 +52720,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>jon_upside_case</t>
+          <t>jon_property_shock</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -49923,7 +52738,7 @@
         <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>26625375</v>
+        <v>18815782.5</v>
       </c>
       <c r="G32" t="n">
         <v>16000000</v>
@@ -49932,10 +52747,10 @@
         <v>2500000</v>
       </c>
       <c r="I32" t="n">
-        <v>8125375.000000004</v>
+        <v>315782.5</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>2600000</v>
+        <v>2150000</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -49944,52 +52759,52 @@
         <v>1200000</v>
       </c>
       <c r="M32" t="n">
-        <v>215000</v>
+        <v>236000</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>1185000</v>
+        <v>714000</v>
       </c>
       <c r="O32" t="n">
-        <v>2.166666666666667</v>
+        <v>1.791666666666667</v>
       </c>
       <c r="P32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>2598196.0625</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>18637762.5</v>
+        <v>13171047.75</v>
       </c>
       <c r="S32" t="n">
-        <v>2637762.5</v>
+        <v>-2828952.25</v>
       </c>
       <c r="T32" t="n">
-        <v>39566.4375</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>2598196.0625</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>2598196.0625</v>
+        <v>0</v>
       </c>
       <c r="W32" s="2" t="n">
-        <v>2598196.0625</v>
+        <v>0</v>
       </c>
       <c r="X32" s="2" t="n">
-        <v>8125375.000000004</v>
+        <v>315782.5</v>
       </c>
       <c r="Y32" s="2" t="n">
-        <v>5527178.937500004</v>
+        <v>315782.5</v>
       </c>
       <c r="Z32" s="2" t="n">
-        <v>8125375.000000004</v>
+        <v>315782.5</v>
       </c>
       <c r="AA32" t="n">
         <v>1000000</v>
       </c>
       <c r="AB32" s="3" t="n">
-        <v>2.321535714285715</v>
+        <v>0.09022357142857143</v>
       </c>
       <c r="AC32" t="n">
         <v>3500000</v>
@@ -50003,7 +52818,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>jon_upside_case</t>
+          <t>jon_property_shock</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -50021,7 +52836,7 @@
         <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>27956643.75</v>
+        <v>19925913.6675</v>
       </c>
       <c r="G33" t="n">
         <v>16000000</v>
@@ -50030,10 +52845,10 @@
         <v>2500000</v>
       </c>
       <c r="I33" t="n">
-        <v>9456643.750000004</v>
+        <v>1425913.6675</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>2704000</v>
+        <v>2214500</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -50042,31 +52857,31 @@
         <v>1200000</v>
       </c>
       <c r="M33" t="n">
-        <v>67600.00000000001</v>
+        <v>88580</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>1436400</v>
+        <v>925920</v>
       </c>
       <c r="O33" t="n">
-        <v>2.253333333333334</v>
+        <v>1.845416666666667</v>
       </c>
       <c r="P33" s="2" t="n">
-        <v>2598196.0625</v>
+        <v>0</v>
       </c>
       <c r="Q33" s="2" t="n">
-        <v>2598196.0625</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>19569650.625</v>
+        <v>13948139.56725</v>
       </c>
       <c r="S33" t="n">
-        <v>971454.5625</v>
+        <v>-2051860.43275</v>
       </c>
       <c r="T33" t="n">
-        <v>14571.8184375</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>956882.7440625</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -50075,19 +52890,19 @@
         <v>0</v>
       </c>
       <c r="X33" s="2" t="n">
-        <v>9456643.750000004</v>
+        <v>1425913.6675</v>
       </c>
       <c r="Y33" s="2" t="n">
-        <v>6858447.687500004</v>
+        <v>1425913.6675</v>
       </c>
       <c r="Z33" s="2" t="n">
-        <v>9456643.750000004</v>
+        <v>1425913.6675</v>
       </c>
       <c r="AA33" t="n">
         <v>1000000</v>
       </c>
       <c r="AB33" s="3" t="n">
-        <v>2.701898214285715</v>
+        <v>0.4074039050000001</v>
       </c>
       <c r="AC33" t="n">
         <v>3500000</v>
@@ -50101,7 +52916,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>jon_upside_case</t>
+          <t>jon_property_shock</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -50119,7 +52934,7 @@
         <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>29354475.93750001</v>
+        <v>21101542.5738825</v>
       </c>
       <c r="G34" t="n">
         <v>16000000</v>
@@ -50128,10 +52943,10 @@
         <v>2500000</v>
       </c>
       <c r="I34" t="n">
-        <v>10854475.93750001</v>
+        <v>2601542.573882498</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>2812160</v>
+        <v>2280935</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -50140,31 +52955,31 @@
         <v>1200000</v>
       </c>
       <c r="M34" t="n">
-        <v>70304</v>
+        <v>91237.40000000001</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>1541856</v>
+        <v>989697.6</v>
       </c>
       <c r="O34" t="n">
-        <v>2.343466666666667</v>
+        <v>1.900779166666667</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>2598196.0625</v>
+        <v>0</v>
       </c>
       <c r="Q34" s="2" t="n">
-        <v>2598196.0625</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>20548133.15625</v>
+        <v>14771079.80171775</v>
       </c>
       <c r="S34" t="n">
-        <v>1949937.093750004</v>
+        <v>-1228920.198282253</v>
       </c>
       <c r="T34" t="n">
-        <v>29249.05640625006</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1920688.037343754</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -50173,24 +52988,906 @@
         <v>0</v>
       </c>
       <c r="X34" s="2" t="n">
-        <v>10854475.93750001</v>
+        <v>2601542.573882498</v>
       </c>
       <c r="Y34" s="2" t="n">
-        <v>8256279.875000007</v>
+        <v>2601542.573882498</v>
       </c>
       <c r="Z34" s="2" t="n">
-        <v>10854475.93750001</v>
+        <v>2601542.573882498</v>
       </c>
       <c r="AA34" t="n">
         <v>1000000</v>
       </c>
       <c r="AB34" s="3" t="n">
-        <v>3.101278839285716</v>
+        <v>0.7432978782521422</v>
       </c>
       <c r="AC34" t="n">
         <v>3500000</v>
       </c>
       <c r="AD34" t="inlineStr">
+        <is>
+          <t>fund_liquidity</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>jon_property_shock</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>jon_deal_1</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>7</v>
+      </c>
+      <c r="D35" t="n">
+        <v>7</v>
+      </c>
+      <c r="E35" t="b">
+        <v>1</v>
+      </c>
+      <c r="F35" t="n">
+        <v>22346533.58574156</v>
+      </c>
+      <c r="G35" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="I35" t="n">
+        <v>3846533.585741565</v>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>2349363.05</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="M35" t="n">
+        <v>93974.522</v>
+      </c>
+      <c r="N35" s="2" t="n">
+        <v>1055388.528</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.957802541666666</v>
+      </c>
+      <c r="P35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>15642573.51001909</v>
+      </c>
+      <c r="S35" t="n">
+        <v>-357426.4899809062</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" s="2" t="n">
+        <v>3846533.585741565</v>
+      </c>
+      <c r="Y35" s="2" t="n">
+        <v>3846533.585741565</v>
+      </c>
+      <c r="Z35" s="2" t="n">
+        <v>3846533.585741565</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="AB35" s="3" t="n">
+        <v>1.099009595926161</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>fund_liquidity</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>jon_property_shock</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>jon_deal_1</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>8</v>
+      </c>
+      <c r="D36" t="n">
+        <v>8</v>
+      </c>
+      <c r="E36" t="b">
+        <v>1</v>
+      </c>
+      <c r="F36" t="n">
+        <v>23664979.06730032</v>
+      </c>
+      <c r="G36" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="I36" t="n">
+        <v>5164979.067300316</v>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>2419843.9415</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="M36" t="n">
+        <v>96793.75766</v>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v>1123050.18384</v>
+      </c>
+      <c r="O36" t="n">
+        <v>2.016536617916667</v>
+      </c>
+      <c r="P36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>16565485.34711022</v>
+      </c>
+      <c r="S36" t="n">
+        <v>565485.3471102193</v>
+      </c>
+      <c r="T36" t="n">
+        <v>14137.13367775548</v>
+      </c>
+      <c r="U36" t="n">
+        <v>551348.2134324638</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" s="2" t="n">
+        <v>5164979.067300316</v>
+      </c>
+      <c r="Y36" s="2" t="n">
+        <v>5164979.067300316</v>
+      </c>
+      <c r="Z36" s="2" t="n">
+        <v>5164979.067300316</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="AB36" s="3" t="n">
+        <v>1.475708304942947</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>fund_liquidity</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>jon_property_shock</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>jon_deal_1</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>9</v>
+      </c>
+      <c r="D37" t="n">
+        <v>9</v>
+      </c>
+      <c r="E37" t="b">
+        <v>1</v>
+      </c>
+      <c r="F37" t="n">
+        <v>24374928.43931933</v>
+      </c>
+      <c r="G37" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="H37" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="I37" t="n">
+        <v>5874928.439319327</v>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>2492439.259745</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="M37" t="n">
+        <v>99697.57038980001</v>
+      </c>
+      <c r="N37" s="2" t="n">
+        <v>1192741.6893552</v>
+      </c>
+      <c r="O37" t="n">
+        <v>2.077032716454167</v>
+      </c>
+      <c r="P37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>17062449.90752353</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1062449.907523528</v>
+      </c>
+      <c r="T37" t="n">
+        <v>26561.24768808819</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1035888.65983544</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" s="2" t="n">
+        <v>5874928.439319327</v>
+      </c>
+      <c r="Y37" s="2" t="n">
+        <v>5874928.439319327</v>
+      </c>
+      <c r="Z37" s="2" t="n">
+        <v>5874928.439319327</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="AB37" s="3" t="n">
+        <v>1.678550982662665</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>fund_liquidity</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>jon_upside_case</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>jon_deal_1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="b">
+        <v>1</v>
+      </c>
+      <c r="F38" t="n">
+        <v>23000000</v>
+      </c>
+      <c r="G38" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="I38" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="M38" t="n">
+        <v>387500</v>
+      </c>
+      <c r="N38" s="2" t="n">
+        <v>-87500</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>16100000</v>
+      </c>
+      <c r="S38" t="n">
+        <v>99999.99999999814</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1499.999999999972</v>
+      </c>
+      <c r="U38" t="n">
+        <v>98499.99999999817</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" s="2" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="Y38" s="2" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="Z38" s="2" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="AB38" s="3" t="n">
+        <v>1.285714285714286</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>fund_liquidity</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>jon_upside_case</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>jon_deal_1</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>2</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E39" t="b">
+        <v>1</v>
+      </c>
+      <c r="F39" t="n">
+        <v>24150000</v>
+      </c>
+      <c r="G39" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="H39" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="I39" t="n">
+        <v>5650000</v>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="M39" t="n">
+        <v>300000</v>
+      </c>
+      <c r="N39" s="2" t="n">
+        <v>500000</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="P39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>16905000</v>
+      </c>
+      <c r="S39" t="n">
+        <v>905000</v>
+      </c>
+      <c r="T39" t="n">
+        <v>13575</v>
+      </c>
+      <c r="U39" t="n">
+        <v>891425</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" s="2" t="n">
+        <v>5650000</v>
+      </c>
+      <c r="Y39" s="2" t="n">
+        <v>5650000</v>
+      </c>
+      <c r="Z39" s="2" t="n">
+        <v>5650000</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="AB39" s="3" t="n">
+        <v>1.614285714285714</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>fund_liquidity</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>jon_upside_case</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>jon_deal_1</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>3</v>
+      </c>
+      <c r="D40" t="n">
+        <v>3</v>
+      </c>
+      <c r="E40" t="b">
+        <v>1</v>
+      </c>
+      <c r="F40" t="n">
+        <v>25357500</v>
+      </c>
+      <c r="G40" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="H40" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="I40" t="n">
+        <v>6857500</v>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="M40" t="n">
+        <v>212500</v>
+      </c>
+      <c r="N40" s="2" t="n">
+        <v>1087500</v>
+      </c>
+      <c r="O40" t="n">
+        <v>2.083333333333333</v>
+      </c>
+      <c r="P40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>17750250</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1750250</v>
+      </c>
+      <c r="T40" t="n">
+        <v>26253.75</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1723996.25</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" s="2" t="n">
+        <v>6857500</v>
+      </c>
+      <c r="Y40" s="2" t="n">
+        <v>6857500</v>
+      </c>
+      <c r="Z40" s="2" t="n">
+        <v>6857500</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="AB40" s="3" t="n">
+        <v>1.959285714285714</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>fund_liquidity</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>jon_upside_case</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>jon_deal_1</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>4</v>
+      </c>
+      <c r="D41" t="n">
+        <v>4</v>
+      </c>
+      <c r="E41" t="b">
+        <v>1</v>
+      </c>
+      <c r="F41" t="n">
+        <v>26625375</v>
+      </c>
+      <c r="G41" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="H41" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="I41" t="n">
+        <v>8125375.000000004</v>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="M41" t="n">
+        <v>215000</v>
+      </c>
+      <c r="N41" s="2" t="n">
+        <v>1185000</v>
+      </c>
+      <c r="O41" t="n">
+        <v>2.166666666666667</v>
+      </c>
+      <c r="P41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="2" t="n">
+        <v>2598196.0625</v>
+      </c>
+      <c r="R41" t="n">
+        <v>18637762.5</v>
+      </c>
+      <c r="S41" t="n">
+        <v>2637762.5</v>
+      </c>
+      <c r="T41" t="n">
+        <v>39566.4375</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2598196.0625</v>
+      </c>
+      <c r="V41" t="n">
+        <v>2598196.0625</v>
+      </c>
+      <c r="W41" s="2" t="n">
+        <v>2598196.0625</v>
+      </c>
+      <c r="X41" s="2" t="n">
+        <v>8125375.000000004</v>
+      </c>
+      <c r="Y41" s="2" t="n">
+        <v>5527178.937500004</v>
+      </c>
+      <c r="Z41" s="2" t="n">
+        <v>8125375.000000004</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="AB41" s="3" t="n">
+        <v>2.321535714285715</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>fund_liquidity</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>jon_upside_case</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>jon_deal_1</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>5</v>
+      </c>
+      <c r="D42" t="n">
+        <v>5</v>
+      </c>
+      <c r="E42" t="b">
+        <v>1</v>
+      </c>
+      <c r="F42" t="n">
+        <v>27956643.75</v>
+      </c>
+      <c r="G42" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="H42" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="I42" t="n">
+        <v>9456643.750000004</v>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>2704000</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="M42" t="n">
+        <v>67600.00000000001</v>
+      </c>
+      <c r="N42" s="2" t="n">
+        <v>1436400</v>
+      </c>
+      <c r="O42" t="n">
+        <v>2.253333333333334</v>
+      </c>
+      <c r="P42" s="2" t="n">
+        <v>2598196.0625</v>
+      </c>
+      <c r="Q42" s="2" t="n">
+        <v>2598196.0625</v>
+      </c>
+      <c r="R42" t="n">
+        <v>19569650.625</v>
+      </c>
+      <c r="S42" t="n">
+        <v>971454.5625</v>
+      </c>
+      <c r="T42" t="n">
+        <v>14571.8184375</v>
+      </c>
+      <c r="U42" t="n">
+        <v>956882.7440625</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" s="2" t="n">
+        <v>9456643.750000004</v>
+      </c>
+      <c r="Y42" s="2" t="n">
+        <v>6858447.687500004</v>
+      </c>
+      <c r="Z42" s="2" t="n">
+        <v>9456643.750000004</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="AB42" s="3" t="n">
+        <v>2.701898214285715</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>fund_liquidity</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>jon_upside_case</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>jon_deal_1</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>6</v>
+      </c>
+      <c r="D43" t="n">
+        <v>6</v>
+      </c>
+      <c r="E43" t="b">
+        <v>1</v>
+      </c>
+      <c r="F43" t="n">
+        <v>29354475.93750001</v>
+      </c>
+      <c r="G43" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="H43" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="I43" t="n">
+        <v>10854475.93750001</v>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>2812160</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="M43" t="n">
+        <v>70304</v>
+      </c>
+      <c r="N43" s="2" t="n">
+        <v>1541856</v>
+      </c>
+      <c r="O43" t="n">
+        <v>2.343466666666667</v>
+      </c>
+      <c r="P43" s="2" t="n">
+        <v>2598196.0625</v>
+      </c>
+      <c r="Q43" s="2" t="n">
+        <v>2598196.0625</v>
+      </c>
+      <c r="R43" t="n">
+        <v>20548133.15625</v>
+      </c>
+      <c r="S43" t="n">
+        <v>1949937.093750004</v>
+      </c>
+      <c r="T43" t="n">
+        <v>29249.05640625006</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1920688.037343754</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" s="2" t="n">
+        <v>10854475.93750001</v>
+      </c>
+      <c r="Y43" s="2" t="n">
+        <v>8256279.875000007</v>
+      </c>
+      <c r="Z43" s="2" t="n">
+        <v>10854475.93750001</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="AB43" s="3" t="n">
+        <v>3.101278839285716</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="AD43" t="inlineStr">
         <is>
           <t>fund_liquidity</t>
         </is>
@@ -50207,7 +53904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D80"/>
+  <dimension ref="A1:D89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -51803,7 +55500,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>jon_upside_case</t>
+          <t>jon_property_shock</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -51818,14 +55515,14 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LP reached 2.00x in year 6.</t>
+          <t>LP reached 2.00x in year 9.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>jon_upside_case</t>
+          <t>jon_property_shock</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -51847,12 +55544,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>jon_upside_case</t>
+          <t>jon_property_shock</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GP_SURVIVABILITY_RISK</t>
+          <t>SLOW_TIME_HORIZON_DRIFT</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -51862,115 +55559,313 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>GP fee income in the early years is below the configured threshold.</t>
+          <t>LP outcome takes a long time or does not arrive within the horizon.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>jon_upside_case</t>
+          <t>jon_property_shock</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>HURDLE_COMPLETION_TRIGGER_EXECUTED</t>
+          <t>GP_SURVIVABILITY_RISK</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Active hurdle completion trigger monetized permitted sources to extinguish LPs.</t>
+          <t>GP fee income in the early years is below the configured threshold.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>jon_upside_case</t>
+          <t>jon_property_shock</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>HURDLE_TRIGGER_ATTEMPTED_BUT_INSUFFICIENT</t>
+          <t>HURDLE_COMPLETION_TRIGGER_EXECUTED</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>info</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Active hurdle completion trigger was eligible, but permitted funding sources were insufficient.</t>
+          <t>Active hurdle completion trigger monetized permitted sources to extinguish LPs.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>jon_upside_case</t>
+          <t>jon_property_shock</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>LP_REDEEMED_VIA_HF_LIQUIDATION</t>
+          <t>HURDLE_TRIGGER_ATTEMPTED_BUT_INSUFFICIENT</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LP hurdle completion used partial hedge fund liquidation.</t>
+          <t>Active hurdle completion trigger was eligible, but permitted funding sources were insufficient.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>jon_upside_case</t>
+          <t>jon_property_shock</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>REFINANCE_EVENT_OCCURRED</t>
+          <t>LP_REDEEMED_VIA_HF_LIQUIDATION</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>One or more configured refinance events generated proceeds.</t>
+          <t>LP hurdle completion used partial hedge fund liquidation.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
+          <t>jon_property_shock</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>LP_REDEEMED_VIA_REFI</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LP hurdle completion used refinance proceeds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>jon_property_shock</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>RE_NAV_IMPAIRMENT</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Real estate NAV fell by more than the configured impairment threshold.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
           <t>jon_upside_case</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>LP_HURDLE_ACHIEVED</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LP reached 2.00x in year 6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>jon_upside_case</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>HURDLE_REACHED_BUT_LIQUIDITY_CONSTRAINED</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Economic hurdle passed before available liquidity could redeem LPs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>jon_upside_case</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>GP_SURVIVABILITY_RISK</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>GP fee income in the early years is below the configured threshold.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>jon_upside_case</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>HURDLE_COMPLETION_TRIGGER_EXECUTED</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Active hurdle completion trigger monetized permitted sources to extinguish LPs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>jon_upside_case</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>HURDLE_TRIGGER_ATTEMPTED_BUT_INSUFFICIENT</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Active hurdle completion trigger was eligible, but permitted funding sources were insufficient.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>jon_upside_case</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>LP_REDEEMED_VIA_HF_LIQUIDATION</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LP hurdle completion used partial hedge fund liquidation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>jon_upside_case</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>REFINANCE_EVENT_OCCURRED</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>One or more configured refinance events generated proceeds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>jon_upside_case</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
         <is>
           <t>LP_GOOD_IRR_GP_LARGE_RESIDUAL</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>LP IRR is attractive while GP residual NAV is large.</t>
         </is>
@@ -52841,7 +56736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -52994,7 +56889,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Equinox on Indian School base case — Sandpainter underwriting Apr 2026. 116-unit Phoenix value-add. $23M purchase, $3.5M equity, $16M new senior + $2.5M assumed liabilities. NOI $1.28M Y1 ramping to $2.15M stabilized. 7.5% IO debt. Refi Y4/Y7 at 70% LTV. HF 13% base. Cashflow routing 60/25/15.</t>
+          <t>Deal 1 base case — 116-unit Class C value-add multifamily, Southwest US. $23M purchase, $3.5M equity, $16M senior + $2.5M assumed liabilities. NOI $1.28M Y1 ramping to $2.15M stabilized. 7.5% IO debt. Refi Y4/Y7 at 70% LTV. HF 13% base. Cashflow routing 60/25/15.</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -53009,7 +56904,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Equinox downside — slower lease-up, lower NOI ramp, higher capex, tighter refi. HF -15% Y1 then recovery.</t>
+          <t>Deal 1 downside — slower lease-up, lower NOI ramp, higher capex, tighter refi. HF -15% Y1 then recovery.</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -53019,15 +56914,30 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>jon_property_shock</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Deal 1 property shock — 25% value drop in Year 2 (market correction), 5-year recovery back to pre-shock trajectory. HF 13% base. Cashflow routing 60/25/15.</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>jon_upside_case</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Equinox upside — faster lease-up, stronger NOI, 5% value growth, better HF returns (25%).</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Deal 1 upside — faster lease-up, stronger NOI, 5% value growth, better HF returns (25%).</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
         <v>20</v>
       </c>
     </row>
@@ -53042,7 +56952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -53391,7 +57301,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Equinox on Indian School base case — Sandpainter underwriting Apr 2026. 116-unit Phoenix value-add. $23M purchase, $3.5M equity, $16M new senior + $2.5M assumed liabilities. NOI $1.28M Y1 ramping to $2.15M stabilized. 7.5% IO debt. Refi Y4/Y7 at 70% LTV. HF 13% base. Cashflow routing 60/25/15.</t>
+          <t>Deal 1 base case — 116-unit Class C value-add multifamily, Southwest US. $23M purchase, $3.5M equity, $16M senior + $2.5M assumed liabilities. NOI $1.28M Y1 ramping to $2.15M stabilized. 7.5% IO debt. Refi Y4/Y7 at 70% LTV. HF 13% base. Cashflow routing 60/25/15.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -53426,7 +57336,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Equinox downside — slower lease-up, lower NOI ramp, higher capex, tighter refi. HF -15% Y1 then recovery.</t>
+          <t>Deal 1 downside — slower lease-up, lower NOI ramp, higher capex, tighter refi. HF -15% Y1 then recovery.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -53456,35 +57366,70 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>jon_property_shock</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Deal 1 property shock — 25% value drop in Year 2 (market correction), 5-year recovery back to pre-shock trajectory. HF 13% base. Cashflow routing 60/25/15.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ideal</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>9116363.636363635</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10800000</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1464975.757575758</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1464975.757575758</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>2.146497575757576</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.09755703872093711</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>jon_upside_case</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Equinox upside — faster lease-up, stronger NOI, 5% value growth, better HF returns (25%).</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Deal 1 upside — faster lease-up, stronger NOI, 5% value growth, better HF returns (25%).</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>ideal</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D13" t="n">
         <v>7610909.09090909</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E13" t="n">
         <v>7200000</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F13" t="n">
         <v>1039363.636363636</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G13" t="n">
         <v>1039363.636363636</v>
       </c>
-      <c r="H12" s="3" t="n">
+      <c r="H13" s="3" t="n">
         <v>2.103936363636364</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I13" t="n">
         <v>0.1432584595516204</v>
       </c>
     </row>
@@ -53499,7 +57444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y152"/>
+  <dimension ref="A1:Y161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -65114,7 +69059,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>jon_upside_case</t>
+          <t>jon_property_shock</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -65148,52 +69093,52 @@
         <v>0</v>
       </c>
       <c r="L147" t="n">
-        <v>-4801818.181818182</v>
+        <v>-5023818.181818182</v>
       </c>
       <c r="M147" t="n">
-        <v>300000</v>
+        <v>78000</v>
       </c>
       <c r="N147" t="n">
-        <v>-4801818.181818182</v>
+        <v>-5023818.181818182</v>
       </c>
       <c r="O147" t="n">
-        <v>111000</v>
+        <v>28860</v>
       </c>
       <c r="P147" t="n">
         <v>0</v>
       </c>
       <c r="Q147" t="n">
-        <v>111000</v>
+        <v>28860</v>
       </c>
       <c r="R147" t="n">
-        <v>111000</v>
+        <v>28860</v>
       </c>
       <c r="S147" s="2" t="n">
         <v>0</v>
       </c>
       <c r="T147" t="n">
-        <v>111000</v>
+        <v>28860</v>
       </c>
       <c r="U147" t="n">
-        <v>111000</v>
+        <v>28860</v>
       </c>
       <c r="V147" s="3" t="n">
-        <v>0.0111</v>
+        <v>0.002886</v>
       </c>
       <c r="W147" s="4" t="n">
-        <v>4801818.181818182</v>
+        <v>5023818.181818182</v>
       </c>
       <c r="X147" t="n">
         <v>0</v>
       </c>
       <c r="Y147" t="n">
-        <v>4801818.181818182</v>
+        <v>5023818.181818182</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>jon_upside_case</t>
+          <t>jon_property_shock</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -65224,55 +69169,55 @@
         <v>8003636.363636363</v>
       </c>
       <c r="K148" t="n">
-        <v>125000</v>
+        <v>0</v>
       </c>
       <c r="L148" t="n">
-        <v>298181.8181818182</v>
+        <v>-133151.5151515153</v>
       </c>
       <c r="M148" t="n">
-        <v>925000</v>
+        <v>368666.6666666665</v>
       </c>
       <c r="N148" t="n">
-        <v>423181.8181818182</v>
+        <v>-133151.5151515153</v>
       </c>
       <c r="O148" t="n">
-        <v>342250</v>
+        <v>136406.6666666666</v>
       </c>
       <c r="P148" t="n">
-        <v>156577.2727272727</v>
+        <v>0</v>
       </c>
       <c r="Q148" t="n">
-        <v>185672.7272727273</v>
+        <v>136406.6666666666</v>
       </c>
       <c r="R148" t="n">
-        <v>296672.7272727273</v>
+        <v>165266.6666666666</v>
       </c>
       <c r="S148" s="2" t="n">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="T148" t="n">
-        <v>485672.7272727273</v>
+        <v>136406.6666666666</v>
       </c>
       <c r="U148" t="n">
-        <v>596672.7272727273</v>
+        <v>165266.6666666666</v>
       </c>
       <c r="V148" s="3" t="n">
-        <v>0.05966727272727273</v>
+        <v>0.01652666666666666</v>
       </c>
       <c r="W148" s="4" t="n">
-        <v>0</v>
+        <v>133151.5151515153</v>
       </c>
       <c r="X148" t="n">
-        <v>125000</v>
+        <v>0</v>
       </c>
       <c r="Y148" t="n">
-        <v>4676818.181818182</v>
+        <v>5156969.696969697</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>jon_upside_case</t>
+          <t>jon_property_shock</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -65303,55 +69248,55 @@
         <v>9705454.545454545</v>
       </c>
       <c r="K149" t="n">
-        <v>271875</v>
+        <v>83739.99999999999</v>
       </c>
       <c r="L149" t="n">
-        <v>798181.8181818181</v>
+        <v>157515.1515151514</v>
       </c>
       <c r="M149" t="n">
-        <v>1571875</v>
+        <v>743073.3333333333</v>
       </c>
       <c r="N149" t="n">
-        <v>1070056.818181818</v>
+        <v>241255.1515151514</v>
       </c>
       <c r="O149" t="n">
-        <v>581593.75</v>
+        <v>274937.1333333333</v>
       </c>
       <c r="P149" t="n">
-        <v>395921.0227272727</v>
+        <v>89264.40606060602</v>
       </c>
       <c r="Q149" t="n">
         <v>185672.7272727273</v>
       </c>
       <c r="R149" t="n">
-        <v>482345.4545454546</v>
+        <v>350939.3939393939</v>
       </c>
       <c r="S149" s="2" t="n">
-        <v>652500</v>
+        <v>200976</v>
       </c>
       <c r="T149" t="n">
-        <v>838172.7272727273</v>
+        <v>386648.7272727273</v>
       </c>
       <c r="U149" t="n">
-        <v>1434845.454545455</v>
+        <v>551915.3939393939</v>
       </c>
       <c r="V149" s="3" t="n">
-        <v>0.1434845454545454</v>
+        <v>0.05519153939393939</v>
       </c>
       <c r="W149" s="4" t="n">
         <v>0</v>
       </c>
       <c r="X149" t="n">
-        <v>271875</v>
+        <v>83739.99999999999</v>
       </c>
       <c r="Y149" t="n">
-        <v>4404943.181818182</v>
+        <v>5073229.696969697</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>jon_upside_case</t>
+          <t>jon_property_shock</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -65382,55 +69327,55 @@
         <v>11407272.72727273</v>
       </c>
       <c r="K150" t="n">
-        <v>296250</v>
+        <v>178500</v>
       </c>
       <c r="L150" t="n">
-        <v>898181.8181818181</v>
+        <v>448181.8181818182</v>
       </c>
       <c r="M150" t="n">
-        <v>1696250</v>
+        <v>1128500</v>
       </c>
       <c r="N150" t="n">
-        <v>1194431.818181818</v>
+        <v>626681.8181818181</v>
       </c>
       <c r="O150" t="n">
-        <v>627612.5</v>
+        <v>417545</v>
       </c>
       <c r="P150" t="n">
-        <v>441939.7727272727</v>
+        <v>231872.2727272727</v>
       </c>
       <c r="Q150" t="n">
         <v>185672.7272727273</v>
       </c>
       <c r="R150" t="n">
-        <v>668018.1818181819</v>
+        <v>536612.1212121212</v>
       </c>
       <c r="S150" s="2" t="n">
-        <v>711000</v>
+        <v>428400</v>
       </c>
       <c r="T150" t="n">
-        <v>896672.7272727273</v>
+        <v>614072.7272727273</v>
       </c>
       <c r="U150" t="n">
-        <v>2331518.181818182</v>
+        <v>1165988.121212121</v>
       </c>
       <c r="V150" s="3" t="n">
-        <v>0.2331518181818182</v>
+        <v>0.1165988121212121</v>
       </c>
       <c r="W150" s="4" t="n">
         <v>0</v>
       </c>
       <c r="X150" t="n">
-        <v>296250</v>
+        <v>178500</v>
       </c>
       <c r="Y150" t="n">
-        <v>4108693.181818182</v>
+        <v>4894729.696969697</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>jon_upside_case</t>
+          <t>jon_property_shock</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -65461,55 +69406,55 @@
         <v>13109090.90909091</v>
       </c>
       <c r="K151" t="n">
-        <v>359100.0000000001</v>
+        <v>231480</v>
       </c>
       <c r="L151" t="n">
-        <v>1002181.818181819</v>
+        <v>512681.8181818182</v>
       </c>
       <c r="M151" t="n">
-        <v>1863100</v>
+        <v>1245980</v>
       </c>
       <c r="N151" t="n">
-        <v>1361281.818181819</v>
+        <v>744161.8181818181</v>
       </c>
       <c r="O151" t="n">
-        <v>689347.0000000001</v>
+        <v>461012.6</v>
       </c>
       <c r="P151" t="n">
-        <v>503674.2727272729</v>
+        <v>275339.8727272727</v>
       </c>
       <c r="Q151" t="n">
-        <v>185672.7272727272</v>
+        <v>185672.7272727273</v>
       </c>
       <c r="R151" t="n">
-        <v>853690.9090909091</v>
+        <v>722284.8484848485</v>
       </c>
       <c r="S151" s="2" t="n">
-        <v>861840.0000000002</v>
+        <v>555552</v>
       </c>
       <c r="T151" t="n">
-        <v>1047512.727272727</v>
+        <v>741224.7272727273</v>
       </c>
       <c r="U151" t="n">
-        <v>3379030.909090909</v>
+        <v>1907212.848484848</v>
       </c>
       <c r="V151" s="3" t="n">
-        <v>0.3379030909090909</v>
+        <v>0.1907212848484848</v>
       </c>
       <c r="W151" s="4" t="n">
         <v>0</v>
       </c>
       <c r="X151" t="n">
-        <v>359100.0000000001</v>
+        <v>231480</v>
       </c>
       <c r="Y151" t="n">
-        <v>3749593.181818182</v>
+        <v>4663249.696969697</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>jon_upside_case</t>
+          <t>jon_property_shock</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -65540,48 +69485,759 @@
         <v>14810909.09090909</v>
       </c>
       <c r="K152" t="n">
+        <v>247424.4</v>
+      </c>
+      <c r="L152" t="n">
+        <v>579116.8181818181</v>
+      </c>
+      <c r="M152" t="n">
+        <v>1328359.4</v>
+      </c>
+      <c r="N152" t="n">
+        <v>826541.2181818181</v>
+      </c>
+      <c r="O152" t="n">
+        <v>491492.9779999999</v>
+      </c>
+      <c r="P152" t="n">
+        <v>305820.2507272727</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>185672.7272727272</v>
+      </c>
+      <c r="R152" t="n">
+        <v>907957.5757575757</v>
+      </c>
+      <c r="S152" s="2" t="n">
+        <v>593818.5599999999</v>
+      </c>
+      <c r="T152" t="n">
+        <v>779491.2872727271</v>
+      </c>
+      <c r="U152" t="n">
+        <v>2686704.135757576</v>
+      </c>
+      <c r="V152" s="3" t="n">
+        <v>0.2686704135757575</v>
+      </c>
+      <c r="W152" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X152" t="n">
+        <v>247424.4</v>
+      </c>
+      <c r="Y152" t="n">
+        <v>4415825.296969697</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>jon_property_shock</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>7</v>
+      </c>
+      <c r="C153" t="n">
+        <v>0</v>
+      </c>
+      <c r="D153" t="n">
+        <v>501818.1818181818</v>
+      </c>
+      <c r="E153" t="n">
+        <v>501818.1818181818</v>
+      </c>
+      <c r="F153" t="n">
+        <v>8112727.272727272</v>
+      </c>
+      <c r="G153" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="H153" t="n">
+        <v>8400000</v>
+      </c>
+      <c r="I153" t="n">
+        <v>1701818.181818182</v>
+      </c>
+      <c r="J153" t="n">
+        <v>16512727.27272727</v>
+      </c>
+      <c r="K153" t="n">
+        <v>263847.132</v>
+      </c>
+      <c r="L153" t="n">
+        <v>647544.8681818179</v>
+      </c>
+      <c r="M153" t="n">
+        <v>1413210.182</v>
+      </c>
+      <c r="N153" t="n">
+        <v>911392.0001818179</v>
+      </c>
+      <c r="O153" t="n">
+        <v>522887.76734</v>
+      </c>
+      <c r="P153" t="n">
+        <v>337215.0400672726</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>185672.7272727274</v>
+      </c>
+      <c r="R153" t="n">
+        <v>1093630.303030303</v>
+      </c>
+      <c r="S153" s="2" t="n">
+        <v>633233.1168</v>
+      </c>
+      <c r="T153" t="n">
+        <v>818905.8440727274</v>
+      </c>
+      <c r="U153" t="n">
+        <v>3505609.979830303</v>
+      </c>
+      <c r="V153" s="3" t="n">
+        <v>0.3505609979830303</v>
+      </c>
+      <c r="W153" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X153" t="n">
+        <v>263847.132</v>
+      </c>
+      <c r="Y153" t="n">
+        <v>4151978.164969697</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>jon_property_shock</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>8</v>
+      </c>
+      <c r="C154" t="n">
+        <v>0</v>
+      </c>
+      <c r="D154" t="n">
+        <v>501818.1818181818</v>
+      </c>
+      <c r="E154" t="n">
+        <v>501818.1818181818</v>
+      </c>
+      <c r="F154" t="n">
+        <v>8614545.454545453</v>
+      </c>
+      <c r="G154" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="H154" t="n">
+        <v>9600000</v>
+      </c>
+      <c r="I154" t="n">
+        <v>1701818.181818182</v>
+      </c>
+      <c r="J154" t="n">
+        <v>18214545.45454545</v>
+      </c>
+      <c r="K154" t="n">
+        <v>280762.54596</v>
+      </c>
+      <c r="L154" t="n">
+        <v>718025.7596818183</v>
+      </c>
+      <c r="M154" t="n">
+        <v>1500606.48746</v>
+      </c>
+      <c r="N154" t="n">
+        <v>998788.3056418183</v>
+      </c>
+      <c r="O154" t="n">
+        <v>555224.4003602002</v>
+      </c>
+      <c r="P154" t="n">
+        <v>369551.6730874728</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>185672.7272727274</v>
+      </c>
+      <c r="R154" t="n">
+        <v>1279303.030303031</v>
+      </c>
+      <c r="S154" s="2" t="n">
+        <v>673830.110304</v>
+      </c>
+      <c r="T154" t="n">
+        <v>859502.8375767274</v>
+      </c>
+      <c r="U154" t="n">
+        <v>4365112.817407031</v>
+      </c>
+      <c r="V154" s="3" t="n">
+        <v>0.4365112817407031</v>
+      </c>
+      <c r="W154" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X154" t="n">
+        <v>280762.54596</v>
+      </c>
+      <c r="Y154" t="n">
+        <v>3871215.619009697</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>jon_property_shock</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>9</v>
+      </c>
+      <c r="C155" t="n">
+        <v>0</v>
+      </c>
+      <c r="D155" t="n">
+        <v>501818.1818181818</v>
+      </c>
+      <c r="E155" t="n">
+        <v>501818.1818181818</v>
+      </c>
+      <c r="F155" t="n">
+        <v>9116363.636363635</v>
+      </c>
+      <c r="G155" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="H155" t="n">
+        <v>10800000</v>
+      </c>
+      <c r="I155" t="n">
+        <v>1701818.181818182</v>
+      </c>
+      <c r="J155" t="n">
+        <v>19916363.63636364</v>
+      </c>
+      <c r="K155" t="n">
+        <v>298185.4223388</v>
+      </c>
+      <c r="L155" t="n">
+        <v>790621.077926818</v>
+      </c>
+      <c r="M155" t="n">
+        <v>1590624.6820838</v>
+      </c>
+      <c r="N155" t="n">
+        <v>1088806.500265618</v>
+      </c>
+      <c r="O155" t="n">
+        <v>588531.132371006</v>
+      </c>
+      <c r="P155" t="n">
+        <v>402858.4050982787</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>185672.7272727272</v>
+      </c>
+      <c r="R155" t="n">
+        <v>1464975.757575758</v>
+      </c>
+      <c r="S155" s="2" t="n">
+        <v>16914190.212896</v>
+      </c>
+      <c r="T155" t="n">
+        <v>17099862.94016873</v>
+      </c>
+      <c r="U155" t="n">
+        <v>21464975.75757576</v>
+      </c>
+      <c r="V155" s="3" t="n">
+        <v>2.146497575757576</v>
+      </c>
+      <c r="W155" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X155" t="n">
+        <v>298185.4223388</v>
+      </c>
+      <c r="Y155" t="n">
+        <v>3573030.196670897</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>jon_upside_case</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>1</v>
+      </c>
+      <c r="C156" t="n">
+        <v>4600000</v>
+      </c>
+      <c r="D156" t="n">
+        <v>501818.1818181818</v>
+      </c>
+      <c r="E156" t="n">
+        <v>5101818.181818182</v>
+      </c>
+      <c r="F156" t="n">
+        <v>5101818.181818182</v>
+      </c>
+      <c r="G156" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="H156" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="I156" t="n">
+        <v>6301818.181818182</v>
+      </c>
+      <c r="J156" t="n">
+        <v>6301818.181818182</v>
+      </c>
+      <c r="K156" t="n">
+        <v>0</v>
+      </c>
+      <c r="L156" t="n">
+        <v>-4801818.181818182</v>
+      </c>
+      <c r="M156" t="n">
+        <v>300000</v>
+      </c>
+      <c r="N156" t="n">
+        <v>-4801818.181818182</v>
+      </c>
+      <c r="O156" t="n">
+        <v>111000</v>
+      </c>
+      <c r="P156" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>111000</v>
+      </c>
+      <c r="R156" t="n">
+        <v>111000</v>
+      </c>
+      <c r="S156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T156" t="n">
+        <v>111000</v>
+      </c>
+      <c r="U156" t="n">
+        <v>111000</v>
+      </c>
+      <c r="V156" s="3" t="n">
+        <v>0.0111</v>
+      </c>
+      <c r="W156" s="4" t="n">
+        <v>4801818.181818182</v>
+      </c>
+      <c r="X156" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y156" t="n">
+        <v>4801818.181818182</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>jon_upside_case</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>2</v>
+      </c>
+      <c r="C157" t="n">
+        <v>0</v>
+      </c>
+      <c r="D157" t="n">
+        <v>501818.1818181818</v>
+      </c>
+      <c r="E157" t="n">
+        <v>501818.1818181818</v>
+      </c>
+      <c r="F157" t="n">
+        <v>5603636.363636363</v>
+      </c>
+      <c r="G157" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="H157" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="I157" t="n">
+        <v>1701818.181818182</v>
+      </c>
+      <c r="J157" t="n">
+        <v>8003636.363636363</v>
+      </c>
+      <c r="K157" t="n">
+        <v>125000</v>
+      </c>
+      <c r="L157" t="n">
+        <v>298181.8181818182</v>
+      </c>
+      <c r="M157" t="n">
+        <v>925000</v>
+      </c>
+      <c r="N157" t="n">
+        <v>423181.8181818182</v>
+      </c>
+      <c r="O157" t="n">
+        <v>342250</v>
+      </c>
+      <c r="P157" t="n">
+        <v>156577.2727272727</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>185672.7272727273</v>
+      </c>
+      <c r="R157" t="n">
+        <v>296672.7272727273</v>
+      </c>
+      <c r="S157" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="T157" t="n">
+        <v>485672.7272727273</v>
+      </c>
+      <c r="U157" t="n">
+        <v>596672.7272727273</v>
+      </c>
+      <c r="V157" s="3" t="n">
+        <v>0.05966727272727273</v>
+      </c>
+      <c r="W157" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X157" t="n">
+        <v>125000</v>
+      </c>
+      <c r="Y157" t="n">
+        <v>4676818.181818182</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>jon_upside_case</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>3</v>
+      </c>
+      <c r="C158" t="n">
+        <v>0</v>
+      </c>
+      <c r="D158" t="n">
+        <v>501818.1818181818</v>
+      </c>
+      <c r="E158" t="n">
+        <v>501818.1818181818</v>
+      </c>
+      <c r="F158" t="n">
+        <v>6105454.545454545</v>
+      </c>
+      <c r="G158" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="H158" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="I158" t="n">
+        <v>1701818.181818182</v>
+      </c>
+      <c r="J158" t="n">
+        <v>9705454.545454545</v>
+      </c>
+      <c r="K158" t="n">
+        <v>271875</v>
+      </c>
+      <c r="L158" t="n">
+        <v>798181.8181818181</v>
+      </c>
+      <c r="M158" t="n">
+        <v>1571875</v>
+      </c>
+      <c r="N158" t="n">
+        <v>1070056.818181818</v>
+      </c>
+      <c r="O158" t="n">
+        <v>581593.75</v>
+      </c>
+      <c r="P158" t="n">
+        <v>395921.0227272727</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>185672.7272727273</v>
+      </c>
+      <c r="R158" t="n">
+        <v>482345.4545454546</v>
+      </c>
+      <c r="S158" s="2" t="n">
+        <v>652500</v>
+      </c>
+      <c r="T158" t="n">
+        <v>838172.7272727273</v>
+      </c>
+      <c r="U158" t="n">
+        <v>1434845.454545455</v>
+      </c>
+      <c r="V158" s="3" t="n">
+        <v>0.1434845454545454</v>
+      </c>
+      <c r="W158" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X158" t="n">
+        <v>271875</v>
+      </c>
+      <c r="Y158" t="n">
+        <v>4404943.181818182</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>jon_upside_case</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>4</v>
+      </c>
+      <c r="C159" t="n">
+        <v>0</v>
+      </c>
+      <c r="D159" t="n">
+        <v>501818.1818181818</v>
+      </c>
+      <c r="E159" t="n">
+        <v>501818.1818181818</v>
+      </c>
+      <c r="F159" t="n">
+        <v>6607272.727272727</v>
+      </c>
+      <c r="G159" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="H159" t="n">
+        <v>4800000</v>
+      </c>
+      <c r="I159" t="n">
+        <v>1701818.181818182</v>
+      </c>
+      <c r="J159" t="n">
+        <v>11407272.72727273</v>
+      </c>
+      <c r="K159" t="n">
+        <v>296250</v>
+      </c>
+      <c r="L159" t="n">
+        <v>898181.8181818181</v>
+      </c>
+      <c r="M159" t="n">
+        <v>1696250</v>
+      </c>
+      <c r="N159" t="n">
+        <v>1194431.818181818</v>
+      </c>
+      <c r="O159" t="n">
+        <v>627612.5</v>
+      </c>
+      <c r="P159" t="n">
+        <v>441939.7727272727</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>185672.7272727273</v>
+      </c>
+      <c r="R159" t="n">
+        <v>668018.1818181819</v>
+      </c>
+      <c r="S159" s="2" t="n">
+        <v>711000</v>
+      </c>
+      <c r="T159" t="n">
+        <v>896672.7272727273</v>
+      </c>
+      <c r="U159" t="n">
+        <v>2331518.181818182</v>
+      </c>
+      <c r="V159" s="3" t="n">
+        <v>0.2331518181818182</v>
+      </c>
+      <c r="W159" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X159" t="n">
+        <v>296250</v>
+      </c>
+      <c r="Y159" t="n">
+        <v>4108693.181818182</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>jon_upside_case</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>5</v>
+      </c>
+      <c r="C160" t="n">
+        <v>0</v>
+      </c>
+      <c r="D160" t="n">
+        <v>501818.1818181818</v>
+      </c>
+      <c r="E160" t="n">
+        <v>501818.1818181818</v>
+      </c>
+      <c r="F160" t="n">
+        <v>7109090.909090908</v>
+      </c>
+      <c r="G160" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="H160" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="I160" t="n">
+        <v>1701818.181818182</v>
+      </c>
+      <c r="J160" t="n">
+        <v>13109090.90909091</v>
+      </c>
+      <c r="K160" t="n">
+        <v>359100.0000000001</v>
+      </c>
+      <c r="L160" t="n">
+        <v>1002181.818181819</v>
+      </c>
+      <c r="M160" t="n">
+        <v>1863100</v>
+      </c>
+      <c r="N160" t="n">
+        <v>1361281.818181819</v>
+      </c>
+      <c r="O160" t="n">
+        <v>689347.0000000001</v>
+      </c>
+      <c r="P160" t="n">
+        <v>503674.2727272729</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>185672.7272727272</v>
+      </c>
+      <c r="R160" t="n">
+        <v>853690.9090909091</v>
+      </c>
+      <c r="S160" s="2" t="n">
+        <v>861840.0000000002</v>
+      </c>
+      <c r="T160" t="n">
+        <v>1047512.727272727</v>
+      </c>
+      <c r="U160" t="n">
+        <v>3379030.909090909</v>
+      </c>
+      <c r="V160" s="3" t="n">
+        <v>0.3379030909090909</v>
+      </c>
+      <c r="W160" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X160" t="n">
+        <v>359100.0000000001</v>
+      </c>
+      <c r="Y160" t="n">
+        <v>3749593.181818182</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>jon_upside_case</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>6</v>
+      </c>
+      <c r="C161" t="n">
+        <v>0</v>
+      </c>
+      <c r="D161" t="n">
+        <v>501818.1818181818</v>
+      </c>
+      <c r="E161" t="n">
+        <v>501818.1818181818</v>
+      </c>
+      <c r="F161" t="n">
+        <v>7610909.09090909</v>
+      </c>
+      <c r="G161" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="H161" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="I161" t="n">
+        <v>1701818.181818182</v>
+      </c>
+      <c r="J161" t="n">
+        <v>14810909.09090909</v>
+      </c>
+      <c r="K161" t="n">
         <v>385464</v>
       </c>
-      <c r="L152" t="n">
+      <c r="L161" t="n">
         <v>1110341.818181818</v>
       </c>
-      <c r="M152" t="n">
+      <c r="M161" t="n">
         <v>1997624</v>
       </c>
-      <c r="N152" t="n">
+      <c r="N161" t="n">
         <v>1495805.818181818</v>
       </c>
-      <c r="O152" t="n">
+      <c r="O161" t="n">
         <v>739120.88</v>
       </c>
-      <c r="P152" t="n">
+      <c r="P161" t="n">
         <v>553448.1527272727</v>
       </c>
-      <c r="Q152" t="n">
+      <c r="Q161" t="n">
         <v>185672.7272727273</v>
       </c>
-      <c r="R152" t="n">
+      <c r="R161" t="n">
         <v>1039363.636363636</v>
       </c>
-      <c r="S152" s="2" t="n">
+      <c r="S161" s="2" t="n">
         <v>17474660</v>
       </c>
-      <c r="T152" t="n">
+      <c r="T161" t="n">
         <v>17660332.72727273</v>
       </c>
-      <c r="U152" t="n">
+      <c r="U161" t="n">
         <v>21039363.63636364</v>
       </c>
-      <c r="V152" s="3" t="n">
+      <c r="V161" s="3" t="n">
         <v>2.103936363636364</v>
       </c>
-      <c r="W152" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X152" t="n">
+      <c r="W161" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X161" t="n">
         <v>385464</v>
       </c>
-      <c r="Y152" t="n">
+      <c r="Y161" t="n">
         <v>3364129.181818182</v>
       </c>
     </row>
